--- a/Hardware/FunciónTransferencia.xlsx
+++ b/Hardware/FunciónTransferencia.xlsx
@@ -79,6 +79,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.00000000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -108,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -117,6 +120,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -179,7 +183,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -520,7 +523,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -646,7 +648,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2392,178 +2393,178 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.6333333333333348E-3</c:v>
+                  <c:v>7.3795833333333335E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8933333333333337E-2</c:v>
+                  <c:v>2.1063333333333333E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.8633333333333337E-2</c:v>
+                  <c:v>3.1854583333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.4766666666666675E-2</c:v>
+                  <c:v>3.8677916666666666E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.9900000000000012E-2</c:v>
+                  <c:v>4.4388750000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.3466666666666674E-2</c:v>
+                  <c:v>4.8356666666666666E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.8066666666666674E-2</c:v>
+                  <c:v>5.347416666666667E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.0633333333333343E-2</c:v>
+                  <c:v>5.6329583333333336E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.2666666666666681E-2</c:v>
+                  <c:v>5.8591666666666674E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.3700000000000012E-2</c:v>
+                  <c:v>5.9741250000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.1633333333333344E-2</c:v>
+                  <c:v>5.7442083333333338E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.2166666666666681E-2</c:v>
+                  <c:v>5.8035416666666673E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.5733333333333343E-2</c:v>
+                  <c:v>6.2003333333333334E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.8300000000000005E-2</c:v>
+                  <c:v>6.4858749999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.8300000000000005E-2</c:v>
+                  <c:v>6.4858749999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.6766666666666681E-2</c:v>
+                  <c:v>6.315291666666667E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.5733333333333343E-2</c:v>
+                  <c:v>6.2003333333333334E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.4200000000000019E-2</c:v>
+                  <c:v>6.0297500000000011E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.5233333333333343E-2</c:v>
+                  <c:v>6.144708333333334E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.623333333333335E-2</c:v>
+                  <c:v>6.2559583333333335E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.4200000000000019E-2</c:v>
+                  <c:v>6.0297500000000011E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.3166666666666675E-2</c:v>
+                  <c:v>5.9147916666666668E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.4700000000000013E-2</c:v>
+                  <c:v>6.0853750000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>5.2666666666666681E-2</c:v>
+                  <c:v>5.8591666666666674E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5.2666666666666681E-2</c:v>
+                  <c:v>5.8591666666666674E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.4700000000000013E-2</c:v>
+                  <c:v>6.0853750000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.623333333333335E-2</c:v>
+                  <c:v>6.2559583333333335E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.3700000000000012E-2</c:v>
+                  <c:v>5.9741250000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.3166666666666675E-2</c:v>
+                  <c:v>5.9147916666666668E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.4200000000000019E-2</c:v>
+                  <c:v>6.0297500000000011E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>5.4200000000000019E-2</c:v>
+                  <c:v>6.0297500000000011E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5.4200000000000019E-2</c:v>
+                  <c:v>6.0297500000000011E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5.4200000000000019E-2</c:v>
+                  <c:v>6.0297500000000011E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5.623333333333335E-2</c:v>
+                  <c:v>6.2559583333333335E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5.7266666666666674E-2</c:v>
+                  <c:v>6.3709166666666664E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>6.136666666666668E-2</c:v>
+                  <c:v>6.8270416666666667E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5.8800000000000012E-2</c:v>
+                  <c:v>6.5415000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5.9833333333333343E-2</c:v>
+                  <c:v>6.656458333333333E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>6.033333333333335E-2</c:v>
+                  <c:v>6.7120833333333338E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>6.0833333333333343E-2</c:v>
+                  <c:v>6.7677083333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>5.8300000000000005E-2</c:v>
+                  <c:v>6.4858749999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>6.1866666666666674E-2</c:v>
+                  <c:v>6.8826666666666661E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>6.1866666666666674E-2</c:v>
+                  <c:v>6.8826666666666661E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>5.9833333333333343E-2</c:v>
+                  <c:v>6.656458333333333E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6.2366666666666681E-2</c:v>
+                  <c:v>6.9382916666666669E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>6.2900000000000011E-2</c:v>
+                  <c:v>6.9976250000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>5.8800000000000012E-2</c:v>
+                  <c:v>6.5415000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>5.9833333333333343E-2</c:v>
+                  <c:v>6.656458333333333E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>5.7766666666666674E-2</c:v>
+                  <c:v>6.4265416666666658E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>5.6766666666666681E-2</c:v>
+                  <c:v>6.315291666666667E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>5.8800000000000012E-2</c:v>
+                  <c:v>6.5415000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>6.136666666666668E-2</c:v>
+                  <c:v>6.8270416666666667E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>6.1866666666666674E-2</c:v>
+                  <c:v>6.8826666666666661E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>5.9833333333333343E-2</c:v>
+                  <c:v>6.656458333333333E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>5.8800000000000012E-2</c:v>
+                  <c:v>6.5415000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>5.8300000000000005E-2</c:v>
+                  <c:v>6.4858749999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>5.7266666666666674E-2</c:v>
+                  <c:v>6.3709166666666664E-2</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>5.9833333333333343E-2</c:v>
+                  <c:v>6.656458333333333E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30850,7 +30851,7 @@
       </c>
       <c r="Z2">
         <f>X2*($A$5/360)</f>
-        <v>3.333333333333334E-3</v>
+        <v>3.7083333333333334E-3</v>
       </c>
       <c r="AB2">
         <v>5000</v>
@@ -30878,7 +30879,7 @@
       </c>
       <c r="AJ2">
         <f>AH2*($A$5/360)</f>
-        <v>4.333333333333334E-3</v>
+        <v>4.8208333333333332E-3</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
@@ -30953,7 +30954,7 @@
       </c>
       <c r="Z3">
         <f t="shared" ref="Z3:Z40" si="9">X3*($A$5/360)</f>
-        <v>2.6600000000000006E-2</v>
+        <v>2.9592500000000004E-2</v>
       </c>
       <c r="AB3">
         <v>10000</v>
@@ -30981,7 +30982,7 @@
       </c>
       <c r="AJ3">
         <f t="shared" ref="AJ3:AJ66" si="13">AH3*($A$5/360)</f>
-        <v>2.8366666666666672E-2</v>
+        <v>3.1557916666666665E-2</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
@@ -31000,7 +31001,7 @@
       </c>
       <c r="F4">
         <f t="shared" si="1"/>
-        <v>6.6333333333333348E-3</v>
+        <v>7.3795833333333335E-3</v>
       </c>
       <c r="H4">
         <v>3000</v>
@@ -31042,7 +31043,7 @@
       </c>
       <c r="U4">
         <f t="shared" si="7"/>
-        <v>5.6333333333333339E-3</v>
+        <v>6.2670833333333337E-3</v>
       </c>
       <c r="W4">
         <v>15000</v>
@@ -31056,7 +31057,7 @@
       </c>
       <c r="Z4">
         <f t="shared" si="9"/>
-        <v>3.553333333333334E-2</v>
+        <v>3.9530833333333334E-2</v>
       </c>
       <c r="AB4">
         <v>15000</v>
@@ -31070,7 +31071,7 @@
       </c>
       <c r="AE4">
         <f t="shared" si="11"/>
-        <v>8.4333333333333343E-3</v>
+        <v>9.3820833333333326E-3</v>
       </c>
       <c r="AG4">
         <v>15000</v>
@@ -31084,13 +31085,13 @@
       </c>
       <c r="AJ4">
         <f t="shared" si="13"/>
-        <v>3.6033333333333341E-2</v>
+        <v>4.0087083333333336E-2</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>A7*A3</f>
-        <v>1.2000000000000002</v>
+        <v>1.335</v>
       </c>
       <c r="C5">
         <v>10000</v>
@@ -31104,7 +31105,7 @@
       </c>
       <c r="F5">
         <f t="shared" si="1"/>
-        <v>1.8933333333333337E-2</v>
+        <v>2.1063333333333333E-2</v>
       </c>
       <c r="H5">
         <v>4000</v>
@@ -31146,7 +31147,7 @@
       </c>
       <c r="U5">
         <f t="shared" si="7"/>
-        <v>2.1466666666666672E-2</v>
+        <v>2.3881666666666669E-2</v>
       </c>
       <c r="W5">
         <v>20000</v>
@@ -31160,7 +31161,7 @@
       </c>
       <c r="Z5">
         <f t="shared" si="9"/>
-        <v>4.013333333333334E-2</v>
+        <v>4.4648333333333332E-2</v>
       </c>
       <c r="AB5">
         <v>20000</v>
@@ -31174,7 +31175,7 @@
       </c>
       <c r="AE5">
         <f t="shared" si="11"/>
-        <v>3.9366666666666675E-2</v>
+        <v>4.379541666666667E-2</v>
       </c>
       <c r="AG5">
         <v>20000</v>
@@ -31188,7 +31189,7 @@
       </c>
       <c r="AJ5">
         <f t="shared" si="13"/>
-        <v>4.423333333333334E-2</v>
+        <v>4.9209583333333334E-2</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
@@ -31207,7 +31208,7 @@
       </c>
       <c r="F6">
         <f t="shared" si="1"/>
-        <v>2.8633333333333337E-2</v>
+        <v>3.1854583333333332E-2</v>
       </c>
       <c r="H6">
         <v>5000</v>
@@ -31249,7 +31250,7 @@
       </c>
       <c r="U6">
         <f t="shared" si="7"/>
-        <v>3.1700000000000006E-2</v>
+        <v>3.5266249999999999E-2</v>
       </c>
       <c r="W6">
         <v>25000</v>
@@ -31263,7 +31264,7 @@
       </c>
       <c r="Z6">
         <f t="shared" si="9"/>
-        <v>5.3433333333333347E-2</v>
+        <v>5.9444583333333342E-2</v>
       </c>
       <c r="AB6">
         <v>25000</v>
@@ -31277,7 +31278,7 @@
       </c>
       <c r="AE6">
         <f t="shared" si="11"/>
-        <v>4.5266666666666677E-2</v>
+        <v>5.035916666666667E-2</v>
       </c>
       <c r="AG6">
         <v>25000</v>
@@ -31291,13 +31292,13 @@
       </c>
       <c r="AJ6">
         <f t="shared" si="13"/>
-        <v>4.7033333333333344E-2</v>
+        <v>5.2324583333333334E-2</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f>0.2</f>
-        <v>0.2</v>
+        <f>0.2225</f>
+        <v>0.2225</v>
       </c>
       <c r="C7">
         <v>15000</v>
@@ -31311,7 +31312,7 @@
       </c>
       <c r="F7">
         <f t="shared" si="1"/>
-        <v>3.4766666666666675E-2</v>
+        <v>3.8677916666666666E-2</v>
       </c>
       <c r="H7">
         <v>6000</v>
@@ -31353,7 +31354,7 @@
       </c>
       <c r="U7">
         <f t="shared" si="7"/>
-        <v>3.8866666666666674E-2</v>
+        <v>4.3239166666666669E-2</v>
       </c>
       <c r="W7">
         <v>30000</v>
@@ -31367,7 +31368,7 @@
       </c>
       <c r="Z7">
         <f t="shared" si="9"/>
-        <v>5.0100000000000006E-2</v>
+        <v>5.5736250000000001E-2</v>
       </c>
       <c r="AB7">
         <v>30000</v>
@@ -31381,7 +31382,7 @@
       </c>
       <c r="AE7">
         <f t="shared" si="11"/>
-        <v>4.7566666666666674E-2</v>
+        <v>5.2917916666666669E-2</v>
       </c>
       <c r="AG7">
         <v>30000</v>
@@ -31395,7 +31396,7 @@
       </c>
       <c r="AJ7">
         <f t="shared" si="13"/>
-        <v>4.5000000000000012E-2</v>
+        <v>5.0062500000000003E-2</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
@@ -31411,7 +31412,7 @@
       </c>
       <c r="F8">
         <f t="shared" si="1"/>
-        <v>3.9900000000000012E-2</v>
+        <v>4.4388750000000005E-2</v>
       </c>
       <c r="H8">
         <v>7000</v>
@@ -31453,7 +31454,7 @@
       </c>
       <c r="U8">
         <f t="shared" si="7"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="W8">
         <v>35000</v>
@@ -31467,7 +31468,7 @@
       </c>
       <c r="Z8">
         <f t="shared" si="9"/>
-        <v>5.6500000000000009E-2</v>
+        <v>6.2856250000000002E-2</v>
       </c>
       <c r="AB8">
         <v>35000</v>
@@ -31481,7 +31482,7 @@
       </c>
       <c r="AE8">
         <f t="shared" si="11"/>
-        <v>5.4700000000000013E-2</v>
+        <v>6.0853750000000005E-2</v>
       </c>
       <c r="AG8">
         <v>35000</v>
@@ -31495,7 +31496,7 @@
       </c>
       <c r="AJ8">
         <f t="shared" si="13"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
@@ -31511,7 +31512,7 @@
       </c>
       <c r="F9">
         <f t="shared" si="1"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="H9">
         <v>8000</v>
@@ -31525,7 +31526,7 @@
       </c>
       <c r="K9">
         <f t="shared" si="3"/>
-        <v>1.266666666666667E-3</v>
+        <v>1.4091666666666666E-3</v>
       </c>
       <c r="M9">
         <v>4000</v>
@@ -31553,7 +31554,7 @@
       </c>
       <c r="U9">
         <f t="shared" si="7"/>
-        <v>4.7033333333333344E-2</v>
+        <v>5.2324583333333334E-2</v>
       </c>
       <c r="W9">
         <v>40000</v>
@@ -31567,7 +31568,7 @@
       </c>
       <c r="Z9">
         <f t="shared" si="9"/>
-        <v>5.8033333333333346E-2</v>
+        <v>6.4562083333333339E-2</v>
       </c>
       <c r="AB9">
         <v>40000</v>
@@ -31581,7 +31582,7 @@
       </c>
       <c r="AE9">
         <f t="shared" si="11"/>
-        <v>5.0366666666666678E-2</v>
+        <v>5.6032916666666668E-2</v>
       </c>
       <c r="AG9">
         <v>40000</v>
@@ -31595,7 +31596,7 @@
       </c>
       <c r="AJ9">
         <f t="shared" si="13"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
@@ -31611,7 +31612,7 @@
       </c>
       <c r="F10">
         <f t="shared" si="1"/>
-        <v>4.8066666666666674E-2</v>
+        <v>5.347416666666667E-2</v>
       </c>
       <c r="H10">
         <v>9000</v>
@@ -31625,7 +31626,7 @@
       </c>
       <c r="K10">
         <f t="shared" si="3"/>
-        <v>3.833333333333334E-3</v>
+        <v>4.2645833333333329E-3</v>
       </c>
       <c r="M10">
         <v>4500</v>
@@ -31653,7 +31654,7 @@
       </c>
       <c r="U10">
         <f t="shared" si="7"/>
-        <v>5.4700000000000013E-2</v>
+        <v>6.0853750000000005E-2</v>
       </c>
       <c r="W10">
         <v>45000</v>
@@ -31667,7 +31668,7 @@
       </c>
       <c r="Z10">
         <f t="shared" si="9"/>
-        <v>5.5233333333333343E-2</v>
+        <v>6.144708333333334E-2</v>
       </c>
       <c r="AB10">
         <v>45000</v>
@@ -31681,7 +31682,7 @@
       </c>
       <c r="AE10">
         <f t="shared" si="11"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="AG10">
         <v>45000</v>
@@ -31695,7 +31696,7 @@
       </c>
       <c r="AJ10">
         <f t="shared" si="13"/>
-        <v>5.1400000000000008E-2</v>
+        <v>5.7182500000000004E-2</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
@@ -31711,7 +31712,7 @@
       </c>
       <c r="F11">
         <f t="shared" si="1"/>
-        <v>5.0633333333333343E-2</v>
+        <v>5.6329583333333336E-2</v>
       </c>
       <c r="H11">
         <v>10000</v>
@@ -31725,7 +31726,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="3"/>
-        <v>1.0233333333333336E-2</v>
+        <v>1.1384583333333333E-2</v>
       </c>
       <c r="M11">
         <v>5000</v>
@@ -31753,7 +31754,7 @@
       </c>
       <c r="U11">
         <f t="shared" si="7"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="W11">
         <v>50000</v>
@@ -31767,7 +31768,7 @@
       </c>
       <c r="Z11">
         <f t="shared" si="9"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="AB11">
         <v>50000</v>
@@ -31781,7 +31782,7 @@
       </c>
       <c r="AE11">
         <f t="shared" si="11"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="AG11">
         <v>50000</v>
@@ -31795,7 +31796,7 @@
       </c>
       <c r="AJ11">
         <f t="shared" si="13"/>
-        <v>5.6500000000000009E-2</v>
+        <v>6.2856250000000002E-2</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
@@ -31811,7 +31812,7 @@
       </c>
       <c r="F12">
         <f t="shared" si="1"/>
-        <v>5.2666666666666681E-2</v>
+        <v>5.8591666666666674E-2</v>
       </c>
       <c r="H12">
         <v>11000</v>
@@ -31825,7 +31826,7 @@
       </c>
       <c r="K12">
         <f t="shared" si="3"/>
-        <v>1.5333333333333336E-2</v>
+        <v>1.7058333333333332E-2</v>
       </c>
       <c r="M12">
         <v>5500</v>
@@ -31853,7 +31854,7 @@
       </c>
       <c r="U12">
         <f t="shared" si="7"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="W12">
         <v>55000</v>
@@ -31867,7 +31868,7 @@
       </c>
       <c r="Z12">
         <f t="shared" si="9"/>
-        <v>5.7266666666666674E-2</v>
+        <v>6.3709166666666664E-2</v>
       </c>
       <c r="AB12">
         <v>55000</v>
@@ -31881,7 +31882,7 @@
       </c>
       <c r="AE12">
         <f t="shared" si="11"/>
-        <v>5.7000000000000016E-2</v>
+        <v>6.3412500000000011E-2</v>
       </c>
       <c r="AG12">
         <v>55000</v>
@@ -31895,7 +31896,7 @@
       </c>
       <c r="AJ12">
         <f t="shared" si="13"/>
-        <v>5.2666666666666681E-2</v>
+        <v>5.8591666666666674E-2</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
@@ -31911,7 +31912,7 @@
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
       <c r="H13">
         <v>12000</v>
@@ -31925,7 +31926,7 @@
       </c>
       <c r="K13">
         <f t="shared" si="3"/>
-        <v>2.3000000000000007E-2</v>
+        <v>2.5587500000000003E-2</v>
       </c>
       <c r="M13">
         <v>6000</v>
@@ -31953,7 +31954,7 @@
       </c>
       <c r="U13">
         <f t="shared" si="7"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="W13">
         <v>60000</v>
@@ -31967,7 +31968,7 @@
       </c>
       <c r="Z13">
         <f t="shared" si="9"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="AB13">
         <v>60000</v>
@@ -31981,7 +31982,7 @@
       </c>
       <c r="AE13">
         <f t="shared" si="11"/>
-        <v>5.6500000000000009E-2</v>
+        <v>6.2856250000000002E-2</v>
       </c>
       <c r="AG13">
         <v>60000</v>
@@ -31995,7 +31996,7 @@
       </c>
       <c r="AJ13">
         <f t="shared" si="13"/>
-        <v>5.9066666666666677E-2</v>
+        <v>6.5711666666666668E-2</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
@@ -32011,7 +32012,7 @@
       </c>
       <c r="F14">
         <f t="shared" si="1"/>
-        <v>5.1633333333333344E-2</v>
+        <v>5.7442083333333338E-2</v>
       </c>
       <c r="H14">
         <v>13000</v>
@@ -32025,7 +32026,7 @@
       </c>
       <c r="K14">
         <f t="shared" si="3"/>
-        <v>2.9400000000000006E-2</v>
+        <v>3.27075E-2</v>
       </c>
       <c r="M14">
         <v>6500</v>
@@ -32053,7 +32054,7 @@
       </c>
       <c r="U14">
         <f t="shared" si="7"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
       <c r="W14">
         <v>65000</v>
@@ -32067,7 +32068,7 @@
       </c>
       <c r="Z14">
         <f t="shared" si="9"/>
-        <v>5.1633333333333344E-2</v>
+        <v>5.7442083333333338E-2</v>
       </c>
       <c r="AB14">
         <v>65000</v>
@@ -32081,7 +32082,7 @@
       </c>
       <c r="AE14">
         <f t="shared" si="11"/>
-        <v>5.9566666666666684E-2</v>
+        <v>6.6267916666666676E-2</v>
       </c>
       <c r="AG14">
         <v>65000</v>
@@ -32095,7 +32096,7 @@
       </c>
       <c r="AJ14">
         <f t="shared" si="13"/>
-        <v>6.4666666666666678E-2</v>
+        <v>7.1941666666666668E-2</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
@@ -32111,7 +32112,7 @@
       </c>
       <c r="F15">
         <f t="shared" si="1"/>
-        <v>5.2166666666666681E-2</v>
+        <v>5.8035416666666673E-2</v>
       </c>
       <c r="H15">
         <v>14000</v>
@@ -32125,7 +32126,7 @@
       </c>
       <c r="K15">
         <f t="shared" si="3"/>
-        <v>3.0666666666666672E-2</v>
+        <v>3.4116666666666663E-2</v>
       </c>
       <c r="M15">
         <v>7000</v>
@@ -32153,7 +32154,7 @@
       </c>
       <c r="U15">
         <f t="shared" si="7"/>
-        <v>6.5433333333333343E-2</v>
+        <v>7.2794583333333329E-2</v>
       </c>
       <c r="W15">
         <v>70000</v>
@@ -32167,7 +32168,7 @@
       </c>
       <c r="Z15">
         <f t="shared" si="9"/>
-        <v>4.8566666666666675E-2</v>
+        <v>5.4030416666666671E-2</v>
       </c>
       <c r="AB15">
         <v>70000</v>
@@ -32181,7 +32182,7 @@
       </c>
       <c r="AE15">
         <f t="shared" si="11"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
       <c r="AG15">
         <v>70000</v>
@@ -32195,7 +32196,7 @@
       </c>
       <c r="AJ15">
         <f t="shared" si="13"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
@@ -32211,7 +32212,7 @@
       </c>
       <c r="F16">
         <f t="shared" si="1"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
       <c r="H16">
         <v>15000</v>
@@ -32225,7 +32226,7 @@
       </c>
       <c r="K16">
         <f t="shared" si="3"/>
-        <v>3.0666666666666672E-2</v>
+        <v>3.4116666666666663E-2</v>
       </c>
       <c r="M16">
         <v>7500</v>
@@ -32253,7 +32254,7 @@
       </c>
       <c r="U16">
         <f t="shared" si="7"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="W16">
         <v>75000</v>
@@ -32267,7 +32268,7 @@
       </c>
       <c r="Z16">
         <f t="shared" si="9"/>
-        <v>5.2400000000000009E-2</v>
+        <v>5.8295000000000007E-2</v>
       </c>
       <c r="AB16">
         <v>75000</v>
@@ -32281,7 +32282,7 @@
       </c>
       <c r="AE16">
         <f t="shared" si="11"/>
-        <v>6.3666666666666677E-2</v>
+        <v>7.0829166666666679E-2</v>
       </c>
       <c r="AG16">
         <v>75000</v>
@@ -32295,7 +32296,7 @@
       </c>
       <c r="AJ16">
         <f t="shared" si="13"/>
-        <v>4.9866666666666677E-2</v>
+        <v>5.5476666666666674E-2</v>
       </c>
     </row>
     <row r="17" spans="3:36" x14ac:dyDescent="0.25">
@@ -32311,7 +32312,7 @@
       </c>
       <c r="F17">
         <f t="shared" si="1"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="H17">
         <v>16000</v>
@@ -32325,7 +32326,7 @@
       </c>
       <c r="K17">
         <f t="shared" si="3"/>
-        <v>3.0666666666666672E-2</v>
+        <v>3.4116666666666663E-2</v>
       </c>
       <c r="M17">
         <v>8000</v>
@@ -32339,7 +32340,7 @@
       </c>
       <c r="P17">
         <f t="shared" si="5"/>
-        <v>2.5666666666666672E-3</v>
+        <v>2.8554166666666667E-3</v>
       </c>
       <c r="R17">
         <v>40000</v>
@@ -32353,7 +32354,7 @@
       </c>
       <c r="U17">
         <f t="shared" si="7"/>
-        <v>6.4433333333333342E-2</v>
+        <v>7.1682083333333327E-2</v>
       </c>
       <c r="W17">
         <v>80000</v>
@@ -32367,7 +32368,7 @@
       </c>
       <c r="Z17">
         <f t="shared" si="9"/>
-        <v>5.4700000000000013E-2</v>
+        <v>6.0853750000000005E-2</v>
       </c>
       <c r="AB17">
         <v>80000</v>
@@ -32381,7 +32382,7 @@
       </c>
       <c r="AE17">
         <f t="shared" si="11"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
       <c r="AG17">
         <v>80000</v>
@@ -32395,7 +32396,7 @@
       </c>
       <c r="AJ17">
         <f t="shared" si="13"/>
-        <v>5.3166666666666675E-2</v>
+        <v>5.9147916666666668E-2</v>
       </c>
     </row>
     <row r="18" spans="3:36" x14ac:dyDescent="0.25">
@@ -32411,7 +32412,7 @@
       </c>
       <c r="F18">
         <f t="shared" si="1"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="H18">
         <v>17000</v>
@@ -32425,7 +32426,7 @@
       </c>
       <c r="K18">
         <f t="shared" si="3"/>
-        <v>3.1966666666666671E-2</v>
+        <v>3.5562916666666666E-2</v>
       </c>
       <c r="M18">
         <v>8500</v>
@@ -32439,7 +32440,7 @@
       </c>
       <c r="P18">
         <f t="shared" si="5"/>
-        <v>5.1000000000000012E-3</v>
+        <v>5.67375E-3</v>
       </c>
       <c r="R18">
         <v>42500</v>
@@ -32453,7 +32454,7 @@
       </c>
       <c r="U18">
         <f t="shared" si="7"/>
-        <v>6.7000000000000018E-2</v>
+        <v>7.4537500000000007E-2</v>
       </c>
       <c r="W18">
         <v>85000</v>
@@ -32467,7 +32468,7 @@
       </c>
       <c r="Z18">
         <f t="shared" si="9"/>
-        <v>5.393333333333334E-2</v>
+        <v>6.0000833333333337E-2</v>
       </c>
       <c r="AB18">
         <v>85000</v>
@@ -32481,7 +32482,7 @@
       </c>
       <c r="AE18">
         <f t="shared" si="11"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="AG18">
         <v>85000</v>
@@ -32495,7 +32496,7 @@
       </c>
       <c r="AJ18">
         <f t="shared" si="13"/>
-        <v>5.9566666666666684E-2</v>
+        <v>6.6267916666666676E-2</v>
       </c>
     </row>
     <row r="19" spans="3:36" x14ac:dyDescent="0.25">
@@ -32511,7 +32512,7 @@
       </c>
       <c r="F19">
         <f t="shared" si="1"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
       <c r="H19">
         <v>18000</v>
@@ -32525,7 +32526,7 @@
       </c>
       <c r="K19">
         <f t="shared" si="3"/>
-        <v>3.5800000000000005E-2</v>
+        <v>3.9827500000000002E-2</v>
       </c>
       <c r="M19">
         <v>9000</v>
@@ -32539,7 +32540,7 @@
       </c>
       <c r="P19">
         <f t="shared" si="5"/>
-        <v>7.666666666666668E-3</v>
+        <v>8.5291666666666658E-3</v>
       </c>
       <c r="R19">
         <v>45000</v>
@@ -32553,7 +32554,7 @@
       </c>
       <c r="U19">
         <f t="shared" si="7"/>
-        <v>6.8533333333333349E-2</v>
+        <v>7.624333333333333E-2</v>
       </c>
       <c r="W19">
         <v>90000</v>
@@ -32567,7 +32568,7 @@
       </c>
       <c r="Z19">
         <f t="shared" si="9"/>
-        <v>5.1900000000000009E-2</v>
+        <v>5.7738750000000005E-2</v>
       </c>
       <c r="AB19">
         <v>90000</v>
@@ -32581,7 +32582,7 @@
       </c>
       <c r="AE19">
         <f t="shared" si="11"/>
-        <v>6.3666666666666677E-2</v>
+        <v>7.0829166666666679E-2</v>
       </c>
       <c r="AG19">
         <v>90000</v>
@@ -32595,7 +32596,7 @@
       </c>
       <c r="AJ19">
         <f t="shared" si="13"/>
-        <v>6.1100000000000008E-2</v>
+        <v>6.7973749999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="3:36" x14ac:dyDescent="0.25">
@@ -32611,7 +32612,7 @@
       </c>
       <c r="F20">
         <f t="shared" si="1"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
       <c r="H20">
         <v>19000</v>
@@ -32625,7 +32626,7 @@
       </c>
       <c r="K20">
         <f t="shared" si="3"/>
-        <v>3.963333333333334E-2</v>
+        <v>4.4092083333333337E-2</v>
       </c>
       <c r="M20">
         <v>9500</v>
@@ -32639,7 +32640,7 @@
       </c>
       <c r="P20">
         <f t="shared" si="5"/>
-        <v>1.2766666666666669E-2</v>
+        <v>1.4202916666666668E-2</v>
       </c>
       <c r="R20">
         <v>47500</v>
@@ -32653,7 +32654,7 @@
       </c>
       <c r="U20">
         <f t="shared" si="7"/>
-        <v>7.056666666666668E-2</v>
+        <v>7.8505416666666675E-2</v>
       </c>
       <c r="W20">
         <v>95000</v>
@@ -32667,7 +32668,7 @@
       </c>
       <c r="Z20">
         <f t="shared" si="9"/>
-        <v>5.5233333333333343E-2</v>
+        <v>6.144708333333334E-2</v>
       </c>
       <c r="AB20">
         <v>95000</v>
@@ -32681,7 +32682,7 @@
       </c>
       <c r="AE20">
         <f t="shared" si="11"/>
-        <v>6.4166666666666677E-2</v>
+        <v>7.1385416666666673E-2</v>
       </c>
       <c r="AG20">
         <v>95000</v>
@@ -32695,7 +32696,7 @@
       </c>
       <c r="AJ20">
         <f t="shared" si="13"/>
-        <v>5.9300000000000005E-2</v>
+        <v>6.5971249999999995E-2</v>
       </c>
     </row>
     <row r="21" spans="3:36" x14ac:dyDescent="0.25">
@@ -32711,7 +32712,7 @@
       </c>
       <c r="F21">
         <f t="shared" si="1"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="H21">
         <v>20000</v>
@@ -32725,7 +32726,7 @@
       </c>
       <c r="K21">
         <f t="shared" si="3"/>
-        <v>4.0900000000000006E-2</v>
+        <v>4.550125E-2</v>
       </c>
       <c r="M21">
         <v>10000</v>
@@ -32739,7 +32740,7 @@
       </c>
       <c r="P21">
         <f t="shared" si="5"/>
-        <v>1.5333333333333336E-2</v>
+        <v>1.7058333333333332E-2</v>
       </c>
       <c r="R21">
         <v>50000</v>
@@ -32753,7 +32754,7 @@
       </c>
       <c r="U21">
         <f t="shared" si="7"/>
-        <v>7.1066666666666681E-2</v>
+        <v>7.9061666666666669E-2</v>
       </c>
       <c r="W21">
         <v>100000</v>
@@ -32767,7 +32768,7 @@
       </c>
       <c r="Z21">
         <f t="shared" si="9"/>
-        <v>6.1100000000000008E-2</v>
+        <v>6.7973749999999999E-2</v>
       </c>
       <c r="AB21">
         <v>100000</v>
@@ -32781,7 +32782,7 @@
       </c>
       <c r="AE21">
         <f t="shared" si="11"/>
-        <v>6.6733333333333339E-2</v>
+        <v>7.4240833333333339E-2</v>
       </c>
       <c r="AG21">
         <v>100000</v>
@@ -32795,7 +32796,7 @@
       </c>
       <c r="AJ21">
         <f t="shared" si="13"/>
-        <v>5.853333333333334E-2</v>
+        <v>6.5118333333333334E-2</v>
       </c>
     </row>
     <row r="22" spans="3:36" x14ac:dyDescent="0.25">
@@ -32811,7 +32812,7 @@
       </c>
       <c r="F22">
         <f t="shared" si="1"/>
-        <v>5.5233333333333343E-2</v>
+        <v>6.144708333333334E-2</v>
       </c>
       <c r="H22">
         <v>21000</v>
@@ -32825,7 +32826,7 @@
       </c>
       <c r="K22">
         <f t="shared" si="3"/>
-        <v>4.473333333333334E-2</v>
+        <v>4.9765833333333336E-2</v>
       </c>
       <c r="M22">
         <v>10500</v>
@@ -32839,7 +32840,7 @@
       </c>
       <c r="P22">
         <f t="shared" si="5"/>
-        <v>1.7900000000000003E-2</v>
+        <v>1.9913750000000001E-2</v>
       </c>
       <c r="R22">
         <v>52500</v>
@@ -32853,7 +32854,7 @@
       </c>
       <c r="U22">
         <f t="shared" si="7"/>
-        <v>6.8533333333333349E-2</v>
+        <v>7.624333333333333E-2</v>
       </c>
       <c r="W22">
         <v>105000</v>
@@ -32867,7 +32868,7 @@
       </c>
       <c r="Z22">
         <f t="shared" si="9"/>
-        <v>5.9066666666666677E-2</v>
+        <v>6.5711666666666668E-2</v>
       </c>
       <c r="AB22">
         <v>105000</v>
@@ -32881,7 +32882,7 @@
       </c>
       <c r="AE22">
         <f t="shared" si="11"/>
-        <v>6.4933333333333343E-2</v>
+        <v>7.2238333333333335E-2</v>
       </c>
       <c r="AG22">
         <v>105000</v>
@@ -32895,7 +32896,7 @@
       </c>
       <c r="AJ22">
         <f t="shared" si="13"/>
-        <v>6.2133333333333346E-2</v>
+        <v>6.9123333333333342E-2</v>
       </c>
     </row>
     <row r="23" spans="3:36" x14ac:dyDescent="0.25">
@@ -32911,7 +32912,7 @@
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="H23">
         <v>22000</v>
@@ -32925,7 +32926,7 @@
       </c>
       <c r="K23">
         <f t="shared" si="3"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="M23">
         <v>11000</v>
@@ -32939,7 +32940,7 @@
       </c>
       <c r="P23">
         <f t="shared" si="5"/>
-        <v>2.0466666666666671E-2</v>
+        <v>2.2769166666666667E-2</v>
       </c>
       <c r="R23">
         <v>55000</v>
@@ -32953,7 +32954,7 @@
       </c>
       <c r="U23">
         <f t="shared" si="7"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
       <c r="W23">
         <v>110000</v>
@@ -32967,7 +32968,7 @@
       </c>
       <c r="Z23">
         <f t="shared" si="9"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="AB23">
         <v>110000</v>
@@ -32981,7 +32982,7 @@
       </c>
       <c r="AE23">
         <f t="shared" si="11"/>
-        <v>6.5200000000000008E-2</v>
+        <v>7.2535000000000002E-2</v>
       </c>
       <c r="AG23">
         <v>110000</v>
@@ -32995,7 +32996,7 @@
       </c>
       <c r="AJ23">
         <f t="shared" si="13"/>
-        <v>6.4666666666666678E-2</v>
+        <v>7.1941666666666668E-2</v>
       </c>
     </row>
     <row r="24" spans="3:36" x14ac:dyDescent="0.25">
@@ -33011,7 +33012,7 @@
       </c>
       <c r="F24">
         <f t="shared" si="1"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="H24">
         <v>23000</v>
@@ -33025,7 +33026,7 @@
       </c>
       <c r="K24">
         <f t="shared" si="3"/>
-        <v>4.7300000000000009E-2</v>
+        <v>5.2621250000000001E-2</v>
       </c>
       <c r="M24">
         <v>11500</v>
@@ -33039,7 +33040,7 @@
       </c>
       <c r="P24">
         <f t="shared" si="5"/>
-        <v>2.3000000000000007E-2</v>
+        <v>2.5587500000000003E-2</v>
       </c>
       <c r="R24">
         <v>57500</v>
@@ -33053,7 +33054,7 @@
       </c>
       <c r="U24">
         <f t="shared" si="7"/>
-        <v>6.5433333333333343E-2</v>
+        <v>7.2794583333333329E-2</v>
       </c>
       <c r="W24">
         <v>115000</v>
@@ -33067,7 +33068,7 @@
       </c>
       <c r="Z24">
         <f t="shared" si="9"/>
-        <v>5.6000000000000015E-2</v>
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="AB24">
         <v>115000</v>
@@ -33081,7 +33082,7 @@
       </c>
       <c r="AE24">
         <f t="shared" si="11"/>
-        <v>6.2133333333333346E-2</v>
+        <v>6.9123333333333342E-2</v>
       </c>
       <c r="AG24">
         <v>115000</v>
@@ -33095,7 +33096,7 @@
       </c>
       <c r="AJ24">
         <f t="shared" si="13"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
     </row>
     <row r="25" spans="3:36" x14ac:dyDescent="0.25">
@@ -33111,7 +33112,7 @@
       </c>
       <c r="F25">
         <f t="shared" si="1"/>
-        <v>5.3166666666666675E-2</v>
+        <v>5.9147916666666668E-2</v>
       </c>
       <c r="H25">
         <v>24000</v>
@@ -33125,7 +33126,7 @@
       </c>
       <c r="K25">
         <f t="shared" si="3"/>
-        <v>4.8566666666666675E-2</v>
+        <v>5.4030416666666671E-2</v>
       </c>
       <c r="M25">
         <v>12000</v>
@@ -33139,7 +33140,7 @@
       </c>
       <c r="P25">
         <f t="shared" si="5"/>
-        <v>2.3000000000000007E-2</v>
+        <v>2.5587500000000003E-2</v>
       </c>
       <c r="R25">
         <v>60000</v>
@@ -33153,7 +33154,7 @@
       </c>
       <c r="U25">
         <f t="shared" si="7"/>
-        <v>6.7000000000000018E-2</v>
+        <v>7.4537500000000007E-2</v>
       </c>
       <c r="W25">
         <v>120000</v>
@@ -33167,7 +33168,7 @@
       </c>
       <c r="Z25">
         <f t="shared" si="9"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
       <c r="AB25">
         <v>120000</v>
@@ -33181,7 +33182,7 @@
       </c>
       <c r="AE25">
         <f t="shared" si="11"/>
-        <v>6.6733333333333339E-2</v>
+        <v>7.4240833333333339E-2</v>
       </c>
       <c r="AG25">
         <v>120000</v>
@@ -33195,7 +33196,7 @@
       </c>
       <c r="AJ25">
         <f t="shared" si="13"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
     </row>
     <row r="26" spans="3:36" x14ac:dyDescent="0.25">
@@ -33211,7 +33212,7 @@
       </c>
       <c r="F26">
         <f t="shared" si="1"/>
-        <v>5.4700000000000013E-2</v>
+        <v>6.0853750000000005E-2</v>
       </c>
       <c r="H26">
         <v>25000</v>
@@ -33225,7 +33226,7 @@
       </c>
       <c r="K26">
         <f t="shared" si="3"/>
-        <v>4.9866666666666677E-2</v>
+        <v>5.5476666666666674E-2</v>
       </c>
       <c r="M26">
         <v>12500</v>
@@ -33239,7 +33240,7 @@
       </c>
       <c r="P26">
         <f t="shared" si="5"/>
-        <v>2.5566666666666672E-2</v>
+        <v>2.8442916666666668E-2</v>
       </c>
       <c r="R26">
         <v>62500</v>
@@ -33253,7 +33254,7 @@
       </c>
       <c r="U26">
         <f t="shared" si="7"/>
-        <v>6.7000000000000018E-2</v>
+        <v>7.4537500000000007E-2</v>
       </c>
       <c r="W26">
         <v>125000</v>
@@ -33267,7 +33268,7 @@
       </c>
       <c r="Z26">
         <f t="shared" si="9"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="AB26">
         <v>125000</v>
@@ -33281,7 +33282,7 @@
       </c>
       <c r="AE26">
         <f t="shared" si="11"/>
-        <v>6.7766666666666669E-2</v>
+        <v>7.5390416666666668E-2</v>
       </c>
       <c r="AG26">
         <v>125000</v>
@@ -33295,7 +33296,7 @@
       </c>
       <c r="AJ26">
         <f t="shared" si="13"/>
-        <v>6.5966666666666673E-2</v>
+        <v>7.3387916666666664E-2</v>
       </c>
     </row>
     <row r="27" spans="3:36" x14ac:dyDescent="0.25">
@@ -33311,7 +33312,7 @@
       </c>
       <c r="F27">
         <f t="shared" si="1"/>
-        <v>5.2666666666666681E-2</v>
+        <v>5.8591666666666674E-2</v>
       </c>
       <c r="H27">
         <v>26000</v>
@@ -33325,7 +33326,7 @@
       </c>
       <c r="K27">
         <f t="shared" si="3"/>
-        <v>5.2400000000000009E-2</v>
+        <v>5.8295000000000007E-2</v>
       </c>
       <c r="M27">
         <v>13000</v>
@@ -33339,7 +33340,7 @@
       </c>
       <c r="P27">
         <f t="shared" si="5"/>
-        <v>2.8133333333333337E-2</v>
+        <v>3.1298333333333331E-2</v>
       </c>
       <c r="R27">
         <v>65000</v>
@@ -33353,7 +33354,7 @@
       </c>
       <c r="U27">
         <f t="shared" si="7"/>
-        <v>6.5966666666666673E-2</v>
+        <v>7.3387916666666664E-2</v>
       </c>
       <c r="W27">
         <v>130000</v>
@@ -33367,7 +33368,7 @@
       </c>
       <c r="Z27">
         <f t="shared" si="9"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
       <c r="AB27">
         <v>130000</v>
@@ -33381,7 +33382,7 @@
       </c>
       <c r="AE27">
         <f t="shared" si="11"/>
-        <v>6.4166666666666677E-2</v>
+        <v>7.1385416666666673E-2</v>
       </c>
       <c r="AG27">
         <v>130000</v>
@@ -33395,7 +33396,7 @@
       </c>
       <c r="AJ27">
         <f t="shared" si="13"/>
-        <v>6.3133333333333347E-2</v>
+        <v>7.0235833333333345E-2</v>
       </c>
     </row>
     <row r="28" spans="3:36" x14ac:dyDescent="0.25">
@@ -33411,7 +33412,7 @@
       </c>
       <c r="F28">
         <f t="shared" si="1"/>
-        <v>5.2666666666666681E-2</v>
+        <v>5.8591666666666674E-2</v>
       </c>
       <c r="H28">
         <v>27000</v>
@@ -33425,7 +33426,7 @@
       </c>
       <c r="K28">
         <f t="shared" si="3"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
       <c r="M28">
         <v>13500</v>
@@ -33439,7 +33440,7 @@
       </c>
       <c r="P28">
         <f t="shared" si="5"/>
-        <v>2.5566666666666672E-2</v>
+        <v>2.8442916666666668E-2</v>
       </c>
       <c r="R28">
         <v>67500</v>
@@ -33453,7 +33454,7 @@
       </c>
       <c r="U28">
         <f t="shared" si="7"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="W28">
         <v>135000</v>
@@ -33467,7 +33468,7 @@
       </c>
       <c r="Z28">
         <f t="shared" si="9"/>
-        <v>5.5466666666666678E-2</v>
+        <v>6.1706666666666674E-2</v>
       </c>
       <c r="AB28">
         <v>135000</v>
@@ -33481,7 +33482,7 @@
       </c>
       <c r="AE28">
         <f t="shared" si="11"/>
-        <v>6.3666666666666677E-2</v>
+        <v>7.0829166666666679E-2</v>
       </c>
       <c r="AG28">
         <v>135000</v>
@@ -33495,7 +33496,7 @@
       </c>
       <c r="AJ28">
         <f t="shared" si="13"/>
-        <v>7.4133333333333343E-2</v>
+        <v>8.2473333333333329E-2</v>
       </c>
     </row>
     <row r="29" spans="3:36" x14ac:dyDescent="0.25">
@@ -33511,7 +33512,7 @@
       </c>
       <c r="F29">
         <f t="shared" si="1"/>
-        <v>5.4700000000000013E-2</v>
+        <v>6.0853750000000005E-2</v>
       </c>
       <c r="H29">
         <v>28000</v>
@@ -33525,7 +33526,7 @@
       </c>
       <c r="K29">
         <f t="shared" si="3"/>
-        <v>5.4966666666666671E-2</v>
+        <v>6.1150416666666665E-2</v>
       </c>
       <c r="M29">
         <v>14000</v>
@@ -33539,7 +33540,7 @@
       </c>
       <c r="P29">
         <f t="shared" si="5"/>
-        <v>3.0666666666666672E-2</v>
+        <v>3.4116666666666663E-2</v>
       </c>
       <c r="R29">
         <v>70000</v>
@@ -33553,7 +33554,7 @@
       </c>
       <c r="U29">
         <f t="shared" si="7"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="W29">
         <v>140000</v>
@@ -33567,7 +33568,7 @@
       </c>
       <c r="Z29">
         <f t="shared" si="9"/>
-        <v>5.853333333333334E-2</v>
+        <v>6.5118333333333334E-2</v>
       </c>
       <c r="AB29">
         <v>140000</v>
@@ -33581,7 +33582,7 @@
       </c>
       <c r="AE29">
         <f t="shared" si="11"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
       <c r="AG29">
         <v>140000</v>
@@ -33595,7 +33596,7 @@
       </c>
       <c r="AJ29">
         <f t="shared" si="13"/>
-        <v>7.4133333333333343E-2</v>
+        <v>8.2473333333333329E-2</v>
       </c>
     </row>
     <row r="30" spans="3:36" x14ac:dyDescent="0.25">
@@ -33611,7 +33612,7 @@
       </c>
       <c r="F30">
         <f t="shared" si="1"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="H30">
         <v>29000</v>
@@ -33625,7 +33626,7 @@
       </c>
       <c r="K30">
         <f t="shared" si="3"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="M30">
         <v>14500</v>
@@ -33639,7 +33640,7 @@
       </c>
       <c r="P30">
         <f t="shared" si="5"/>
-        <v>3.0666666666666672E-2</v>
+        <v>3.4116666666666663E-2</v>
       </c>
       <c r="R30">
         <v>72500</v>
@@ -33653,7 +33654,7 @@
       </c>
       <c r="U30">
         <f t="shared" si="7"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="W30">
         <v>145000</v>
@@ -33667,7 +33668,7 @@
       </c>
       <c r="Z30">
         <f t="shared" si="9"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="AB30">
         <v>145000</v>
@@ -33681,7 +33682,7 @@
       </c>
       <c r="AE30">
         <f t="shared" si="11"/>
-        <v>6.2633333333333346E-2</v>
+        <v>6.9679583333333336E-2</v>
       </c>
       <c r="AG30">
         <v>145000</v>
@@ -33695,7 +33696,7 @@
       </c>
       <c r="AJ30">
         <f t="shared" si="13"/>
-        <v>6.7500000000000018E-2</v>
+        <v>7.5093750000000001E-2</v>
       </c>
     </row>
     <row r="31" spans="3:36" x14ac:dyDescent="0.25">
@@ -33711,7 +33712,7 @@
       </c>
       <c r="F31">
         <f t="shared" si="1"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
       <c r="H31">
         <v>30000</v>
@@ -33725,7 +33726,7 @@
       </c>
       <c r="K31">
         <f t="shared" si="3"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M31">
         <v>15000</v>
@@ -33739,7 +33740,7 @@
       </c>
       <c r="P31">
         <f t="shared" si="5"/>
-        <v>3.0666666666666672E-2</v>
+        <v>3.4116666666666663E-2</v>
       </c>
       <c r="R31">
         <v>75000</v>
@@ -33753,7 +33754,7 @@
       </c>
       <c r="U31">
         <f t="shared" si="7"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="W31">
         <v>150000</v>
@@ -33767,7 +33768,7 @@
       </c>
       <c r="Z31">
         <f t="shared" si="9"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
       <c r="AB31">
         <v>150000</v>
@@ -33781,7 +33782,7 @@
       </c>
       <c r="AE31">
         <f t="shared" si="11"/>
-        <v>6.4933333333333343E-2</v>
+        <v>7.2238333333333335E-2</v>
       </c>
       <c r="AG31">
         <v>150000</v>
@@ -33795,7 +33796,7 @@
       </c>
       <c r="AJ31">
         <f t="shared" si="13"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
     </row>
     <row r="32" spans="3:36" x14ac:dyDescent="0.25">
@@ -33811,7 +33812,7 @@
       </c>
       <c r="F32">
         <f t="shared" si="1"/>
-        <v>5.3166666666666675E-2</v>
+        <v>5.9147916666666668E-2</v>
       </c>
       <c r="H32">
         <v>31000</v>
@@ -33825,7 +33826,7 @@
       </c>
       <c r="K32">
         <f t="shared" si="3"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="M32">
         <v>15500</v>
@@ -33839,7 +33840,7 @@
       </c>
       <c r="P32">
         <f t="shared" si="5"/>
-        <v>3.0666666666666672E-2</v>
+        <v>3.4116666666666663E-2</v>
       </c>
       <c r="R32">
         <v>77500</v>
@@ -33853,7 +33854,7 @@
       </c>
       <c r="U32">
         <f t="shared" si="7"/>
-        <v>6.4933333333333343E-2</v>
+        <v>7.2238333333333335E-2</v>
       </c>
       <c r="W32">
         <v>155000</v>
@@ -33867,7 +33868,7 @@
       </c>
       <c r="Z32">
         <f t="shared" si="9"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="AB32">
         <v>155000</v>
@@ -33881,7 +33882,7 @@
       </c>
       <c r="AE32">
         <f t="shared" si="11"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="AG32">
         <v>155000</v>
@@ -33895,7 +33896,7 @@
       </c>
       <c r="AJ32">
         <f t="shared" si="13"/>
-        <v>5.6500000000000009E-2</v>
+        <v>6.2856250000000002E-2</v>
       </c>
     </row>
     <row r="33" spans="3:36" x14ac:dyDescent="0.25">
@@ -33911,7 +33912,7 @@
       </c>
       <c r="F33">
         <f t="shared" si="1"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="H33">
         <v>32000</v>
@@ -33925,7 +33926,7 @@
       </c>
       <c r="K33">
         <f t="shared" ref="K33:K81" si="15">I33*($A$5/360)</f>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M33">
         <v>16000</v>
@@ -33939,7 +33940,7 @@
       </c>
       <c r="P33">
         <f t="shared" si="5"/>
-        <v>3.3233333333333344E-2</v>
+        <v>3.6972083333333336E-2</v>
       </c>
       <c r="R33">
         <v>80000</v>
@@ -33953,7 +33954,7 @@
       </c>
       <c r="U33">
         <f t="shared" si="7"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
       <c r="W33">
         <v>160000</v>
@@ -33967,7 +33968,7 @@
       </c>
       <c r="Z33">
         <f t="shared" si="9"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="AB33">
         <v>160000</v>
@@ -33981,7 +33982,7 @@
       </c>
       <c r="AE33">
         <f t="shared" si="11"/>
-        <v>6.1600000000000016E-2</v>
+        <v>6.8530000000000008E-2</v>
       </c>
       <c r="AG33">
         <v>160000</v>
@@ -33995,7 +33996,7 @@
       </c>
       <c r="AJ33">
         <f t="shared" si="13"/>
-        <v>7.236666666666669E-2</v>
+        <v>8.0507916666666679E-2</v>
       </c>
     </row>
     <row r="34" spans="3:36" x14ac:dyDescent="0.25">
@@ -34011,7 +34012,7 @@
       </c>
       <c r="F34">
         <f t="shared" si="1"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="H34">
         <v>33000</v>
@@ -34025,7 +34026,7 @@
       </c>
       <c r="K34">
         <f t="shared" si="15"/>
-        <v>5.4966666666666671E-2</v>
+        <v>6.1150416666666665E-2</v>
       </c>
       <c r="M34">
         <v>16500</v>
@@ -34039,7 +34040,7 @@
       </c>
       <c r="P34">
         <f t="shared" si="5"/>
-        <v>3.3233333333333344E-2</v>
+        <v>3.6972083333333336E-2</v>
       </c>
       <c r="R34">
         <v>82500</v>
@@ -34053,7 +34054,7 @@
       </c>
       <c r="U34">
         <f t="shared" si="7"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="W34">
         <v>165000</v>
@@ -34067,7 +34068,7 @@
       </c>
       <c r="Z34">
         <f t="shared" si="9"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
       <c r="AB34">
         <v>165000</v>
@@ -34081,7 +34082,7 @@
       </c>
       <c r="AE34">
         <f t="shared" si="11"/>
-        <v>5.9066666666666677E-2</v>
+        <v>6.5711666666666668E-2</v>
       </c>
       <c r="AG34">
         <v>165000</v>
@@ -34095,7 +34096,7 @@
       </c>
       <c r="AJ34">
         <f t="shared" si="13"/>
-        <v>7.236666666666669E-2</v>
+        <v>8.0507916666666679E-2</v>
       </c>
     </row>
     <row r="35" spans="3:36" x14ac:dyDescent="0.25">
@@ -34111,7 +34112,7 @@
       </c>
       <c r="F35">
         <f t="shared" si="1"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="H35">
         <v>34000</v>
@@ -34125,7 +34126,7 @@
       </c>
       <c r="K35">
         <f t="shared" si="15"/>
-        <v>5.4966666666666671E-2</v>
+        <v>6.1150416666666665E-2</v>
       </c>
       <c r="M35">
         <v>17000</v>
@@ -34139,7 +34140,7 @@
       </c>
       <c r="P35">
         <f t="shared" si="5"/>
-        <v>3.3233333333333344E-2</v>
+        <v>3.6972083333333336E-2</v>
       </c>
       <c r="R35">
         <v>85000</v>
@@ -34153,7 +34154,7 @@
       </c>
       <c r="U35">
         <f t="shared" si="7"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="W35">
         <v>170000</v>
@@ -34167,7 +34168,7 @@
       </c>
       <c r="Z35">
         <f t="shared" si="9"/>
-        <v>6.1600000000000016E-2</v>
+        <v>6.8530000000000008E-2</v>
       </c>
       <c r="AB35">
         <v>170000</v>
@@ -34181,7 +34182,7 @@
       </c>
       <c r="AE35">
         <f t="shared" si="11"/>
-        <v>6.3133333333333347E-2</v>
+        <v>7.0235833333333345E-2</v>
       </c>
       <c r="AG35">
         <v>170000</v>
@@ -34195,7 +34196,7 @@
       </c>
       <c r="AJ35">
         <f t="shared" si="13"/>
-        <v>6.5966666666666673E-2</v>
+        <v>7.3387916666666664E-2</v>
       </c>
     </row>
     <row r="36" spans="3:36" x14ac:dyDescent="0.25">
@@ -34211,7 +34212,7 @@
       </c>
       <c r="F36">
         <f t="shared" si="1"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="H36">
         <v>35000</v>
@@ -34225,7 +34226,7 @@
       </c>
       <c r="K36">
         <f t="shared" si="15"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M36">
         <v>17500</v>
@@ -34239,7 +34240,7 @@
       </c>
       <c r="P36">
         <f t="shared" si="5"/>
-        <v>3.3233333333333344E-2</v>
+        <v>3.6972083333333336E-2</v>
       </c>
       <c r="R36">
         <v>87500</v>
@@ -34253,7 +34254,7 @@
       </c>
       <c r="U36">
         <f t="shared" si="7"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="W36">
         <v>175000</v>
@@ -34267,7 +34268,7 @@
       </c>
       <c r="Z36">
         <f t="shared" si="9"/>
-        <v>6.8000000000000005E-2</v>
+        <v>7.5649999999999995E-2</v>
       </c>
       <c r="AB36">
         <v>175000</v>
@@ -34281,7 +34282,7 @@
       </c>
       <c r="AE36">
         <f t="shared" si="11"/>
-        <v>6.1600000000000016E-2</v>
+        <v>6.8530000000000008E-2</v>
       </c>
       <c r="AG36">
         <v>175000</v>
@@ -34295,7 +34296,7 @@
       </c>
       <c r="AJ36">
         <f t="shared" si="13"/>
-        <v>6.2133333333333346E-2</v>
+        <v>6.9123333333333342E-2</v>
       </c>
     </row>
     <row r="37" spans="3:36" x14ac:dyDescent="0.25">
@@ -34311,7 +34312,7 @@
       </c>
       <c r="F37">
         <f t="shared" si="1"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="H37">
         <v>36000</v>
@@ -34325,7 +34326,7 @@
       </c>
       <c r="K37">
         <f t="shared" si="15"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M37">
         <v>18000</v>
@@ -34339,7 +34340,7 @@
       </c>
       <c r="P37">
         <f t="shared" si="5"/>
-        <v>3.5800000000000005E-2</v>
+        <v>3.9827500000000002E-2</v>
       </c>
       <c r="R37">
         <v>90000</v>
@@ -34353,7 +34354,7 @@
       </c>
       <c r="U37">
         <f t="shared" si="7"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="W37">
         <v>180000</v>
@@ -34367,7 +34368,7 @@
       </c>
       <c r="Z37">
         <f t="shared" si="9"/>
-        <v>6.3400000000000012E-2</v>
+        <v>7.0532499999999998E-2</v>
       </c>
       <c r="AB37">
         <v>180000</v>
@@ -34381,7 +34382,7 @@
       </c>
       <c r="AE37">
         <f t="shared" si="11"/>
-        <v>5.853333333333334E-2</v>
+        <v>6.5118333333333334E-2</v>
       </c>
       <c r="AG37">
         <v>180000</v>
@@ -34395,7 +34396,7 @@
       </c>
       <c r="AJ37">
         <f t="shared" si="13"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
     </row>
     <row r="38" spans="3:36" x14ac:dyDescent="0.25">
@@ -34411,7 +34412,7 @@
       </c>
       <c r="F38">
         <f t="shared" si="1"/>
-        <v>5.7266666666666674E-2</v>
+        <v>6.3709166666666664E-2</v>
       </c>
       <c r="H38">
         <v>37000</v>
@@ -34425,7 +34426,7 @@
       </c>
       <c r="K38">
         <f t="shared" si="15"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="M38">
         <v>18500</v>
@@ -34439,7 +34440,7 @@
       </c>
       <c r="P38">
         <f t="shared" si="5"/>
-        <v>3.8366666666666674E-2</v>
+        <v>4.2682916666666668E-2</v>
       </c>
       <c r="R38">
         <v>92500</v>
@@ -34453,7 +34454,7 @@
       </c>
       <c r="U38">
         <f t="shared" si="7"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="W38">
         <v>185000</v>
@@ -34467,7 +34468,7 @@
       </c>
       <c r="Z38">
         <f t="shared" si="9"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="AB38">
         <v>185000</v>
@@ -34481,7 +34482,7 @@
       </c>
       <c r="AE38">
         <f t="shared" si="11"/>
-        <v>5.6500000000000009E-2</v>
+        <v>6.2856250000000002E-2</v>
       </c>
       <c r="AG38">
         <v>185000</v>
@@ -34495,7 +34496,7 @@
       </c>
       <c r="AJ38">
         <f t="shared" si="13"/>
-        <v>6.1100000000000008E-2</v>
+        <v>6.7973749999999999E-2</v>
       </c>
     </row>
     <row r="39" spans="3:36" x14ac:dyDescent="0.25">
@@ -34511,7 +34512,7 @@
       </c>
       <c r="F39">
         <f t="shared" si="1"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
       <c r="H39">
         <v>38000</v>
@@ -34525,7 +34526,7 @@
       </c>
       <c r="K39">
         <f t="shared" si="15"/>
-        <v>5.4966666666666671E-2</v>
+        <v>6.1150416666666665E-2</v>
       </c>
       <c r="M39">
         <v>19000</v>
@@ -34539,7 +34540,7 @@
       </c>
       <c r="P39">
         <f t="shared" si="5"/>
-        <v>3.5800000000000005E-2</v>
+        <v>3.9827500000000002E-2</v>
       </c>
       <c r="R39">
         <v>95000</v>
@@ -34553,7 +34554,7 @@
       </c>
       <c r="U39">
         <f t="shared" si="7"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
       <c r="W39">
         <v>190000</v>
@@ -34567,7 +34568,7 @@
       </c>
       <c r="Z39">
         <f t="shared" si="9"/>
-        <v>6.1100000000000008E-2</v>
+        <v>6.7973749999999999E-2</v>
       </c>
       <c r="AB39">
         <v>190000</v>
@@ -34581,7 +34582,7 @@
       </c>
       <c r="AE39">
         <f t="shared" si="11"/>
-        <v>5.6500000000000009E-2</v>
+        <v>6.2856250000000002E-2</v>
       </c>
       <c r="AG39">
         <v>190000</v>
@@ -34595,7 +34596,7 @@
       </c>
       <c r="AJ39">
         <f t="shared" si="13"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
     </row>
     <row r="40" spans="3:36" x14ac:dyDescent="0.25">
@@ -34611,7 +34612,7 @@
       </c>
       <c r="F40">
         <f t="shared" si="1"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="H40">
         <v>39000</v>
@@ -34625,7 +34626,7 @@
       </c>
       <c r="K40">
         <f t="shared" si="15"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
       <c r="M40">
         <v>19500</v>
@@ -34639,7 +34640,7 @@
       </c>
       <c r="P40">
         <f t="shared" si="5"/>
-        <v>3.8366666666666674E-2</v>
+        <v>4.2682916666666668E-2</v>
       </c>
       <c r="R40">
         <v>97500</v>
@@ -34653,7 +34654,7 @@
       </c>
       <c r="U40">
         <f t="shared" si="7"/>
-        <v>5.9300000000000005E-2</v>
+        <v>6.5971249999999995E-2</v>
       </c>
       <c r="W40">
         <v>195000</v>
@@ -34667,7 +34668,7 @@
       </c>
       <c r="Z40">
         <f t="shared" si="9"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="AB40">
         <v>195000</v>
@@ -34681,7 +34682,7 @@
       </c>
       <c r="AE40">
         <f t="shared" si="11"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
       <c r="AG40">
         <v>195000</v>
@@ -34695,7 +34696,7 @@
       </c>
       <c r="AJ40">
         <f t="shared" si="13"/>
-        <v>6.2633333333333346E-2</v>
+        <v>6.9679583333333336E-2</v>
       </c>
     </row>
     <row r="41" spans="3:36" x14ac:dyDescent="0.25">
@@ -34711,7 +34712,7 @@
       </c>
       <c r="F41">
         <f t="shared" si="1"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="H41">
         <v>40000</v>
@@ -34725,7 +34726,7 @@
       </c>
       <c r="K41">
         <f t="shared" si="15"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
       <c r="M41">
         <v>20000</v>
@@ -34739,7 +34740,7 @@
       </c>
       <c r="P41">
         <f t="shared" si="5"/>
-        <v>3.8333333333333344E-2</v>
+        <v>4.2645833333333334E-2</v>
       </c>
       <c r="AG41">
         <v>200000</v>
@@ -34753,7 +34754,7 @@
       </c>
       <c r="AJ41">
         <f t="shared" si="13"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
     </row>
     <row r="42" spans="3:36" x14ac:dyDescent="0.25">
@@ -34769,7 +34770,7 @@
       </c>
       <c r="F42">
         <f t="shared" si="1"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
       <c r="H42">
         <v>41000</v>
@@ -34783,7 +34784,7 @@
       </c>
       <c r="K42">
         <f t="shared" si="15"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
       <c r="M42">
         <v>20500</v>
@@ -34797,19 +34798,19 @@
       </c>
       <c r="P42">
         <f t="shared" si="5"/>
-        <v>4.0900000000000006E-2</v>
+        <v>4.550125E-2</v>
       </c>
       <c r="U42">
         <f>AVERAGE(U25:U40)</f>
-        <v>6.1870833333333333E-2</v>
+        <v>6.8831302083333323E-2</v>
       </c>
       <c r="Z42">
         <f>AVERAGE(Z17:Z40)</f>
-        <v>5.8831944444444451E-2</v>
+        <v>6.5450538194444449E-2</v>
       </c>
       <c r="AE42">
         <f>AVERAGE(AE17:AE40)</f>
-        <v>6.2506944444444448E-2</v>
+        <v>6.9538975694444449E-2</v>
       </c>
       <c r="AG42">
         <v>205000</v>
@@ -34823,7 +34824,7 @@
       </c>
       <c r="AJ42">
         <f t="shared" si="13"/>
-        <v>5.7000000000000016E-2</v>
+        <v>6.3412500000000011E-2</v>
       </c>
     </row>
     <row r="43" spans="3:36" x14ac:dyDescent="0.25">
@@ -34839,7 +34840,7 @@
       </c>
       <c r="F43">
         <f t="shared" si="1"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="H43">
         <v>42000</v>
@@ -34853,7 +34854,7 @@
       </c>
       <c r="K43">
         <f t="shared" si="15"/>
-        <v>6.2633333333333346E-2</v>
+        <v>6.9679583333333336E-2</v>
       </c>
       <c r="M43">
         <v>21000</v>
@@ -34867,19 +34868,19 @@
       </c>
       <c r="P43">
         <f t="shared" si="5"/>
-        <v>4.0900000000000006E-2</v>
+        <v>4.550125E-2</v>
       </c>
       <c r="U43">
         <f>_xlfn.VAR.P(U25:U40)</f>
-        <v>8.1274826388889022E-6</v>
+        <v>1.0059029684787345E-5</v>
       </c>
       <c r="Z43">
         <f>_xlfn.VAR.P(Z17:Z40)</f>
-        <v>1.1458470293209872E-5</v>
+        <v>1.4181647373830517E-5</v>
       </c>
       <c r="AE43">
         <f>_xlfn.VAR.P(AE17:AE40)</f>
-        <v>8.7217573302469068E-6</v>
+        <v>1.0794537470763412E-5</v>
       </c>
       <c r="AG43">
         <v>210000</v>
@@ -34893,7 +34894,7 @@
       </c>
       <c r="AJ43">
         <f t="shared" si="13"/>
-        <v>6.3133333333333347E-2</v>
+        <v>7.0235833333333345E-2</v>
       </c>
     </row>
     <row r="44" spans="3:36" x14ac:dyDescent="0.25">
@@ -34909,7 +34910,7 @@
       </c>
       <c r="F44">
         <f t="shared" si="1"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="H44">
         <v>43000</v>
@@ -34923,7 +34924,7 @@
       </c>
       <c r="K44">
         <f t="shared" si="15"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="M44">
         <v>21500</v>
@@ -34937,7 +34938,7 @@
       </c>
       <c r="P44">
         <f t="shared" si="5"/>
-        <v>4.0900000000000006E-2</v>
+        <v>4.550125E-2</v>
       </c>
       <c r="AG44">
         <v>215000</v>
@@ -34951,7 +34952,7 @@
       </c>
       <c r="AJ44">
         <f t="shared" si="13"/>
-        <v>5.8033333333333346E-2</v>
+        <v>6.4562083333333339E-2</v>
       </c>
     </row>
     <row r="45" spans="3:36" x14ac:dyDescent="0.25">
@@ -34967,7 +34968,7 @@
       </c>
       <c r="F45">
         <f t="shared" si="1"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="H45">
         <v>44000</v>
@@ -34981,7 +34982,7 @@
       </c>
       <c r="K45">
         <f t="shared" si="15"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="M45">
         <v>22000</v>
@@ -34995,7 +34996,7 @@
       </c>
       <c r="P45">
         <f t="shared" si="5"/>
-        <v>3.8366666666666674E-2</v>
+        <v>4.2682916666666668E-2</v>
       </c>
       <c r="AG45">
         <v>220000</v>
@@ -35009,7 +35010,7 @@
       </c>
       <c r="AJ45">
         <f t="shared" si="13"/>
-        <v>5.7000000000000016E-2</v>
+        <v>6.3412500000000011E-2</v>
       </c>
     </row>
     <row r="46" spans="3:36" x14ac:dyDescent="0.25">
@@ -35025,7 +35026,7 @@
       </c>
       <c r="F46">
         <f t="shared" si="1"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="H46">
         <v>45000</v>
@@ -35039,7 +35040,7 @@
       </c>
       <c r="K46">
         <f t="shared" si="15"/>
-        <v>6.2633333333333346E-2</v>
+        <v>6.9679583333333336E-2</v>
       </c>
       <c r="M46">
         <v>22500</v>
@@ -35053,7 +35054,7 @@
       </c>
       <c r="P46">
         <f t="shared" si="5"/>
-        <v>4.0900000000000006E-2</v>
+        <v>4.550125E-2</v>
       </c>
       <c r="AG46">
         <v>225000</v>
@@ -35067,7 +35068,7 @@
       </c>
       <c r="AJ46">
         <f t="shared" si="13"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
     </row>
     <row r="47" spans="3:36" x14ac:dyDescent="0.25">
@@ -35083,7 +35084,7 @@
       </c>
       <c r="F47">
         <f t="shared" si="1"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="H47">
         <v>46000</v>
@@ -35097,7 +35098,7 @@
       </c>
       <c r="K47">
         <f t="shared" si="15"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="M47">
         <v>23000</v>
@@ -35111,7 +35112,7 @@
       </c>
       <c r="P47">
         <f t="shared" si="5"/>
-        <v>4.0900000000000006E-2</v>
+        <v>4.550125E-2</v>
       </c>
       <c r="AG47">
         <v>230000</v>
@@ -35125,7 +35126,7 @@
       </c>
       <c r="AJ47">
         <f t="shared" si="13"/>
-        <v>5.7266666666666674E-2</v>
+        <v>6.3709166666666664E-2</v>
       </c>
     </row>
     <row r="48" spans="3:36" x14ac:dyDescent="0.25">
@@ -35141,7 +35142,7 @@
       </c>
       <c r="F48">
         <f t="shared" si="1"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
       <c r="H48">
         <v>47000</v>
@@ -35155,7 +35156,7 @@
       </c>
       <c r="K48">
         <f t="shared" si="15"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
       <c r="M48">
         <v>23500</v>
@@ -35169,7 +35170,7 @@
       </c>
       <c r="P48">
         <f t="shared" si="5"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="AG48">
         <v>235000</v>
@@ -35183,7 +35184,7 @@
       </c>
       <c r="AJ48">
         <f t="shared" si="13"/>
-        <v>6.3666666666666677E-2</v>
+        <v>7.0829166666666679E-2</v>
       </c>
     </row>
     <row r="49" spans="3:36" x14ac:dyDescent="0.25">
@@ -35199,7 +35200,7 @@
       </c>
       <c r="F49">
         <f t="shared" si="1"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
       <c r="H49">
         <v>48000</v>
@@ -35213,7 +35214,7 @@
       </c>
       <c r="K49">
         <f t="shared" si="15"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="M49">
         <v>24000</v>
@@ -35227,7 +35228,7 @@
       </c>
       <c r="P49">
         <f t="shared" si="5"/>
-        <v>4.0900000000000006E-2</v>
+        <v>4.550125E-2</v>
       </c>
       <c r="AG49">
         <v>240000</v>
@@ -35241,7 +35242,7 @@
       </c>
       <c r="AJ49">
         <f t="shared" si="13"/>
-        <v>5.853333333333334E-2</v>
+        <v>6.5118333333333334E-2</v>
       </c>
     </row>
     <row r="50" spans="3:36" x14ac:dyDescent="0.25">
@@ -35257,7 +35258,7 @@
       </c>
       <c r="F50">
         <f t="shared" si="1"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="H50">
         <v>49000</v>
@@ -35271,7 +35272,7 @@
       </c>
       <c r="K50">
         <f t="shared" si="15"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
       <c r="M50">
         <v>24500</v>
@@ -35285,7 +35286,7 @@
       </c>
       <c r="P50">
         <f t="shared" si="5"/>
-        <v>4.0900000000000006E-2</v>
+        <v>4.550125E-2</v>
       </c>
       <c r="AG50">
         <v>245000</v>
@@ -35299,7 +35300,7 @@
       </c>
       <c r="AJ50">
         <f t="shared" si="13"/>
-        <v>5.6000000000000015E-2</v>
+        <v>6.2300000000000001E-2</v>
       </c>
     </row>
     <row r="51" spans="3:36" x14ac:dyDescent="0.25">
@@ -35315,7 +35316,7 @@
       </c>
       <c r="F51">
         <f t="shared" si="1"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="H51">
         <v>50000</v>
@@ -35329,7 +35330,7 @@
       </c>
       <c r="K51">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M51">
         <v>25000</v>
@@ -35343,7 +35344,7 @@
       </c>
       <c r="P51">
         <f t="shared" si="5"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="AG51">
         <v>250000</v>
@@ -35357,7 +35358,7 @@
       </c>
       <c r="AJ51">
         <f t="shared" si="13"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="52" spans="3:36" x14ac:dyDescent="0.25">
@@ -35373,7 +35374,7 @@
       </c>
       <c r="F52">
         <f t="shared" si="1"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
       <c r="H52">
         <v>51000</v>
@@ -35387,7 +35388,7 @@
       </c>
       <c r="K52">
         <f t="shared" si="15"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="M52">
         <v>25500</v>
@@ -35401,7 +35402,7 @@
       </c>
       <c r="P52">
         <f t="shared" si="5"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="AG52">
         <v>255000</v>
@@ -35415,7 +35416,7 @@
       </c>
       <c r="AJ52">
         <f t="shared" si="13"/>
-        <v>6.8533333333333349E-2</v>
+        <v>7.624333333333333E-2</v>
       </c>
     </row>
     <row r="53" spans="3:36" x14ac:dyDescent="0.25">
@@ -35431,7 +35432,7 @@
       </c>
       <c r="F53">
         <f t="shared" si="1"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
       <c r="H53">
         <v>52000</v>
@@ -35445,7 +35446,7 @@
       </c>
       <c r="K53">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M53">
         <v>26000</v>
@@ -35459,7 +35460,7 @@
       </c>
       <c r="P53">
         <f t="shared" si="5"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="AG53">
         <v>260000</v>
@@ -35473,7 +35474,7 @@
       </c>
       <c r="AJ53">
         <f t="shared" si="13"/>
-        <v>6.4433333333333342E-2</v>
+        <v>7.1682083333333327E-2</v>
       </c>
     </row>
     <row r="54" spans="3:36" x14ac:dyDescent="0.25">
@@ -35489,7 +35490,7 @@
       </c>
       <c r="F54">
         <f t="shared" si="1"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="H54">
         <v>53000</v>
@@ -35503,7 +35504,7 @@
       </c>
       <c r="K54">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M54">
         <v>26500</v>
@@ -35517,7 +35518,7 @@
       </c>
       <c r="P54">
         <f t="shared" si="5"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="AG54">
         <v>265000</v>
@@ -35531,7 +35532,7 @@
       </c>
       <c r="AJ54">
         <f t="shared" si="13"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
     </row>
     <row r="55" spans="3:36" x14ac:dyDescent="0.25">
@@ -35547,7 +35548,7 @@
       </c>
       <c r="F55">
         <f t="shared" si="1"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
       <c r="H55">
         <v>54000</v>
@@ -35561,7 +35562,7 @@
       </c>
       <c r="K55">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M55">
         <v>27000</v>
@@ -35575,7 +35576,7 @@
       </c>
       <c r="P55">
         <f t="shared" si="5"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG55">
         <v>270000</v>
@@ -35589,7 +35590,7 @@
       </c>
       <c r="AJ55">
         <f t="shared" si="13"/>
-        <v>5.4466666666666677E-2</v>
+        <v>6.0594166666666671E-2</v>
       </c>
     </row>
     <row r="56" spans="3:36" x14ac:dyDescent="0.25">
@@ -35605,7 +35606,7 @@
       </c>
       <c r="F56">
         <f t="shared" si="1"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="H56">
         <v>55000</v>
@@ -35619,7 +35620,7 @@
       </c>
       <c r="K56">
         <f t="shared" si="15"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="M56">
         <v>27500</v>
@@ -35633,7 +35634,7 @@
       </c>
       <c r="P56">
         <f t="shared" si="5"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="AG56">
         <v>275000</v>
@@ -35647,7 +35648,7 @@
       </c>
       <c r="AJ56">
         <f t="shared" si="13"/>
-        <v>6.1100000000000008E-2</v>
+        <v>6.7973749999999999E-2</v>
       </c>
     </row>
     <row r="57" spans="3:36" x14ac:dyDescent="0.25">
@@ -35663,7 +35664,7 @@
       </c>
       <c r="F57">
         <f t="shared" si="1"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="H57">
         <v>56000</v>
@@ -35677,7 +35678,7 @@
       </c>
       <c r="K57">
         <f t="shared" si="15"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M57">
         <v>28000</v>
@@ -35691,7 +35692,7 @@
       </c>
       <c r="P57">
         <f t="shared" si="5"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="AG57">
         <v>280000</v>
@@ -35705,7 +35706,7 @@
       </c>
       <c r="AJ57">
         <f t="shared" si="13"/>
-        <v>6.9300000000000014E-2</v>
+        <v>7.7096250000000005E-2</v>
       </c>
     </row>
     <row r="58" spans="3:36" x14ac:dyDescent="0.25">
@@ -35721,7 +35722,7 @@
       </c>
       <c r="F58">
         <f t="shared" si="1"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="H58">
         <v>57000</v>
@@ -35735,7 +35736,7 @@
       </c>
       <c r="K58">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M58">
         <v>28500</v>
@@ -35749,7 +35750,7 @@
       </c>
       <c r="P58">
         <f t="shared" si="5"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG58">
         <v>285000</v>
@@ -35763,7 +35764,7 @@
       </c>
       <c r="AJ58">
         <f t="shared" si="13"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
     </row>
     <row r="59" spans="3:36" x14ac:dyDescent="0.25">
@@ -35779,7 +35780,7 @@
       </c>
       <c r="F59">
         <f t="shared" si="1"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="H59">
         <v>58000</v>
@@ -35793,7 +35794,7 @@
       </c>
       <c r="K59">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M59">
         <v>29000</v>
@@ -35807,7 +35808,7 @@
       </c>
       <c r="P59">
         <f t="shared" si="5"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="AG59">
         <v>290000</v>
@@ -35821,7 +35822,7 @@
       </c>
       <c r="AJ59">
         <f t="shared" si="13"/>
-        <v>6.3133333333333347E-2</v>
+        <v>7.0235833333333345E-2</v>
       </c>
     </row>
     <row r="60" spans="3:36" x14ac:dyDescent="0.25">
@@ -35837,7 +35838,7 @@
       </c>
       <c r="F60">
         <f t="shared" si="1"/>
-        <v>5.7266666666666674E-2</v>
+        <v>6.3709166666666664E-2</v>
       </c>
       <c r="H60">
         <v>59000</v>
@@ -35851,7 +35852,7 @@
       </c>
       <c r="K60">
         <f t="shared" si="15"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="M60">
         <v>29500</v>
@@ -35865,7 +35866,7 @@
       </c>
       <c r="P60">
         <f t="shared" si="5"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG60">
         <v>295000</v>
@@ -35879,7 +35880,7 @@
       </c>
       <c r="AJ60">
         <f t="shared" si="13"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
     </row>
     <row r="61" spans="3:36" x14ac:dyDescent="0.25">
@@ -35895,7 +35896,7 @@
       </c>
       <c r="F61">
         <f t="shared" si="1"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="H61">
         <v>60000</v>
@@ -35909,7 +35910,7 @@
       </c>
       <c r="K61">
         <f t="shared" si="15"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
       <c r="M61">
         <v>30000</v>
@@ -35923,7 +35924,7 @@
       </c>
       <c r="P61">
         <f t="shared" si="5"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG61">
         <v>300000</v>
@@ -35937,7 +35938,7 @@
       </c>
       <c r="AJ61">
         <f t="shared" si="13"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
     </row>
     <row r="62" spans="3:36" x14ac:dyDescent="0.25">
@@ -35953,7 +35954,7 @@
       </c>
       <c r="F62">
         <f t="shared" si="1"/>
-        <v>6.5433333333333343E-2</v>
+        <v>7.2794583333333329E-2</v>
       </c>
       <c r="H62">
         <v>61000</v>
@@ -35967,7 +35968,7 @@
       </c>
       <c r="K62">
         <f t="shared" si="15"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
       <c r="M62">
         <v>30500</v>
@@ -35981,7 +35982,7 @@
       </c>
       <c r="P62">
         <f t="shared" si="5"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG62">
         <v>305000</v>
@@ -35995,7 +35996,7 @@
       </c>
       <c r="AJ62">
         <f t="shared" si="13"/>
-        <v>7.6700000000000018E-2</v>
+        <v>8.5328750000000009E-2</v>
       </c>
     </row>
     <row r="63" spans="3:36" x14ac:dyDescent="0.25">
@@ -36011,7 +36012,7 @@
       </c>
       <c r="F63">
         <f t="shared" si="1"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
       <c r="H63">
         <v>62000</v>
@@ -36025,7 +36026,7 @@
       </c>
       <c r="K63">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M63">
         <v>31000</v>
@@ -36039,7 +36040,7 @@
       </c>
       <c r="P63">
         <f t="shared" si="5"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG63">
         <v>310000</v>
@@ -36053,7 +36054,7 @@
       </c>
       <c r="AJ63">
         <f t="shared" si="13"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
     </row>
     <row r="64" spans="3:36" x14ac:dyDescent="0.25">
@@ -36069,7 +36070,7 @@
       </c>
       <c r="F64">
         <f t="shared" si="1"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
       <c r="H64">
         <v>63000</v>
@@ -36083,7 +36084,7 @@
       </c>
       <c r="K64">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M64">
         <v>31500</v>
@@ -36097,7 +36098,7 @@
       </c>
       <c r="P64">
         <f t="shared" si="5"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG64">
         <v>315000</v>
@@ -36111,7 +36112,7 @@
       </c>
       <c r="AJ64">
         <f t="shared" si="13"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
     </row>
     <row r="65" spans="3:36" x14ac:dyDescent="0.25">
@@ -36127,7 +36128,7 @@
       </c>
       <c r="F65">
         <f t="shared" si="1"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
       <c r="H65">
         <v>64000</v>
@@ -36141,7 +36142,7 @@
       </c>
       <c r="K65">
         <f t="shared" si="15"/>
-        <v>6.2633333333333346E-2</v>
+        <v>6.9679583333333336E-2</v>
       </c>
       <c r="M65">
         <v>32000</v>
@@ -36155,7 +36156,7 @@
       </c>
       <c r="P65">
         <f t="shared" si="5"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG65">
         <v>320000</v>
@@ -36169,7 +36170,7 @@
       </c>
       <c r="AJ65">
         <f t="shared" si="13"/>
-        <v>6.7500000000000018E-2</v>
+        <v>7.5093750000000001E-2</v>
       </c>
     </row>
     <row r="66" spans="3:36" x14ac:dyDescent="0.25">
@@ -36185,7 +36186,7 @@
       </c>
       <c r="F66">
         <f t="shared" si="1"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="H66">
         <v>65000</v>
@@ -36199,7 +36200,7 @@
       </c>
       <c r="K66">
         <f t="shared" si="15"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
       <c r="M66">
         <v>32500</v>
@@ -36213,7 +36214,7 @@
       </c>
       <c r="P66">
         <f t="shared" si="5"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG66">
         <v>325000</v>
@@ -36227,7 +36228,7 @@
       </c>
       <c r="AJ66">
         <f t="shared" si="13"/>
-        <v>6.0600000000000008E-2</v>
+        <v>6.7417500000000005E-2</v>
       </c>
     </row>
     <row r="67" spans="3:36" x14ac:dyDescent="0.25">
@@ -36243,7 +36244,7 @@
       </c>
       <c r="F67">
         <f t="shared" ref="F67:F130" si="17">D67*($A$5/360)</f>
-        <v>6.9033333333333349E-2</v>
+        <v>7.6799583333333338E-2</v>
       </c>
       <c r="H67">
         <v>66000</v>
@@ -36257,7 +36258,7 @@
       </c>
       <c r="K67">
         <f t="shared" si="15"/>
-        <v>6.9033333333333349E-2</v>
+        <v>7.6799583333333338E-2</v>
       </c>
       <c r="M67">
         <v>33000</v>
@@ -36271,7 +36272,7 @@
       </c>
       <c r="P67">
         <f t="shared" ref="P67:P100" si="19">N67*($A$5/360)</f>
-        <v>4.8566666666666675E-2</v>
+        <v>5.4030416666666671E-2</v>
       </c>
       <c r="AG67">
         <v>330000</v>
@@ -36285,7 +36286,7 @@
       </c>
       <c r="AJ67">
         <f t="shared" ref="AJ67:AJ70" si="21">AH67*($A$5/360)</f>
-        <v>7.7733333333333349E-2</v>
+        <v>8.6478333333333338E-2</v>
       </c>
     </row>
     <row r="68" spans="3:36" x14ac:dyDescent="0.25">
@@ -36301,7 +36302,7 @@
       </c>
       <c r="F68">
         <f t="shared" si="17"/>
-        <v>7.056666666666668E-2</v>
+        <v>7.8505416666666675E-2</v>
       </c>
       <c r="H68">
         <v>67000</v>
@@ -36315,7 +36316,7 @@
       </c>
       <c r="K68">
         <f t="shared" si="15"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
       <c r="M68">
         <v>33500</v>
@@ -36329,7 +36330,7 @@
       </c>
       <c r="P68">
         <f t="shared" si="19"/>
-        <v>4.8566666666666675E-2</v>
+        <v>5.4030416666666671E-2</v>
       </c>
       <c r="AG68">
         <v>335000</v>
@@ -36343,7 +36344,7 @@
       </c>
       <c r="AJ68">
         <f t="shared" si="21"/>
-        <v>6.7766666666666669E-2</v>
+        <v>7.5390416666666668E-2</v>
       </c>
     </row>
     <row r="69" spans="3:36" x14ac:dyDescent="0.25">
@@ -36359,7 +36360,7 @@
       </c>
       <c r="F69">
         <f t="shared" si="17"/>
-        <v>6.5433333333333343E-2</v>
+        <v>7.2794583333333329E-2</v>
       </c>
       <c r="H69">
         <v>68000</v>
@@ -36373,7 +36374,7 @@
       </c>
       <c r="K69">
         <f t="shared" si="15"/>
-        <v>6.5200000000000008E-2</v>
+        <v>7.2535000000000002E-2</v>
       </c>
       <c r="M69">
         <v>34000</v>
@@ -36387,7 +36388,7 @@
       </c>
       <c r="P69">
         <f t="shared" si="19"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG69">
         <v>340000</v>
@@ -36401,7 +36402,7 @@
       </c>
       <c r="AJ69">
         <f t="shared" si="21"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="70" spans="3:36" x14ac:dyDescent="0.25">
@@ -36417,7 +36418,7 @@
       </c>
       <c r="F70">
         <f t="shared" si="17"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
       <c r="H70">
         <v>69000</v>
@@ -36431,7 +36432,7 @@
       </c>
       <c r="K70">
         <f t="shared" si="15"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="M70">
         <v>34500</v>
@@ -36445,7 +36446,7 @@
       </c>
       <c r="P70">
         <f t="shared" si="19"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AG70">
         <v>345000</v>
@@ -36459,7 +36460,7 @@
       </c>
       <c r="AJ70">
         <f t="shared" si="21"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
     </row>
     <row r="71" spans="3:36" x14ac:dyDescent="0.25">
@@ -36475,7 +36476,7 @@
       </c>
       <c r="F71">
         <f t="shared" si="17"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
       <c r="H71">
         <v>70000</v>
@@ -36489,7 +36490,7 @@
       </c>
       <c r="K71">
         <f t="shared" si="15"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
       <c r="M71">
         <v>35000</v>
@@ -36503,7 +36504,7 @@
       </c>
       <c r="P71">
         <f t="shared" si="19"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
     </row>
     <row r="72" spans="3:36" x14ac:dyDescent="0.25">
@@ -36519,7 +36520,7 @@
       </c>
       <c r="F72">
         <f t="shared" si="17"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="H72">
         <v>71000</v>
@@ -36533,7 +36534,7 @@
       </c>
       <c r="K72">
         <f t="shared" si="15"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
       <c r="M72">
         <v>35500</v>
@@ -36547,11 +36548,11 @@
       </c>
       <c r="P72">
         <f t="shared" si="19"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
       <c r="AJ72">
         <f>AVERAGE(AJ17:AJ70)</f>
-        <v>6.283950617283951E-2</v>
+        <v>6.9908950617283944E-2</v>
       </c>
     </row>
     <row r="73" spans="3:36" x14ac:dyDescent="0.25">
@@ -36567,7 +36568,7 @@
       </c>
       <c r="F73">
         <f t="shared" si="17"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
       <c r="H73">
         <v>72000</v>
@@ -36581,7 +36582,7 @@
       </c>
       <c r="K73">
         <f t="shared" si="15"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="M73">
         <v>36000</v>
@@ -36595,11 +36596,11 @@
       </c>
       <c r="P73">
         <f t="shared" si="19"/>
-        <v>4.3466666666666674E-2</v>
+        <v>4.8356666666666666E-2</v>
       </c>
       <c r="AJ73">
         <f>_xlfn.VAR.P(AJ17:AJ70)</f>
-        <v>3.1766134735558614E-5</v>
+        <v>3.931555519380619E-5</v>
       </c>
     </row>
     <row r="74" spans="3:36" x14ac:dyDescent="0.25">
@@ -36615,7 +36616,7 @@
       </c>
       <c r="F74">
         <f t="shared" si="17"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="H74">
         <v>73000</v>
@@ -36629,7 +36630,7 @@
       </c>
       <c r="K74">
         <f t="shared" si="15"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M74">
         <v>36500</v>
@@ -36643,7 +36644,7 @@
       </c>
       <c r="P74">
         <f t="shared" si="19"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
     </row>
     <row r="75" spans="3:36" x14ac:dyDescent="0.25">
@@ -36659,7 +36660,7 @@
       </c>
       <c r="F75">
         <f t="shared" si="17"/>
-        <v>6.4433333333333342E-2</v>
+        <v>7.1682083333333327E-2</v>
       </c>
       <c r="H75">
         <v>74000</v>
@@ -36673,7 +36674,7 @@
       </c>
       <c r="K75">
         <f t="shared" si="15"/>
-        <v>5.4966666666666671E-2</v>
+        <v>6.1150416666666665E-2</v>
       </c>
       <c r="M75">
         <v>37000</v>
@@ -36687,7 +36688,7 @@
       </c>
       <c r="P75">
         <f t="shared" si="19"/>
-        <v>4.6033333333333343E-2</v>
+        <v>5.1212083333333339E-2</v>
       </c>
     </row>
     <row r="76" spans="3:36" x14ac:dyDescent="0.25">
@@ -36703,7 +36704,7 @@
       </c>
       <c r="F76">
         <f t="shared" si="17"/>
-        <v>6.4433333333333342E-2</v>
+        <v>7.1682083333333327E-2</v>
       </c>
       <c r="H76">
         <v>75000</v>
@@ -36717,7 +36718,7 @@
       </c>
       <c r="K76">
         <f t="shared" si="15"/>
-        <v>5.4966666666666671E-2</v>
+        <v>6.1150416666666665E-2</v>
       </c>
       <c r="M76">
         <v>37500</v>
@@ -36731,7 +36732,7 @@
       </c>
       <c r="P76">
         <f t="shared" si="19"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="77" spans="3:36" x14ac:dyDescent="0.25">
@@ -36747,7 +36748,7 @@
       </c>
       <c r="F77">
         <f t="shared" si="17"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
       <c r="H77">
         <v>76000</v>
@@ -36761,7 +36762,7 @@
       </c>
       <c r="K77">
         <f t="shared" si="15"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
       <c r="M77">
         <v>38000</v>
@@ -36775,7 +36776,7 @@
       </c>
       <c r="P77">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="78" spans="3:36" x14ac:dyDescent="0.25">
@@ -36791,7 +36792,7 @@
       </c>
       <c r="F78">
         <f t="shared" si="17"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="H78">
         <v>77000</v>
@@ -36805,7 +36806,7 @@
       </c>
       <c r="K78">
         <f t="shared" si="15"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M78">
         <v>38500</v>
@@ -36819,7 +36820,7 @@
       </c>
       <c r="P78">
         <f t="shared" si="19"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="79" spans="3:36" x14ac:dyDescent="0.25">
@@ -36835,7 +36836,7 @@
       </c>
       <c r="F79">
         <f t="shared" si="17"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="H79">
         <v>78000</v>
@@ -36849,7 +36850,7 @@
       </c>
       <c r="K79">
         <f t="shared" si="15"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M79">
         <v>39000</v>
@@ -36863,7 +36864,7 @@
       </c>
       <c r="P79">
         <f t="shared" si="19"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="80" spans="3:36" x14ac:dyDescent="0.25">
@@ -36879,7 +36880,7 @@
       </c>
       <c r="F80">
         <f t="shared" si="17"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="H80">
         <v>79000</v>
@@ -36893,7 +36894,7 @@
       </c>
       <c r="K80">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M80">
         <v>39500</v>
@@ -36907,7 +36908,7 @@
       </c>
       <c r="P80">
         <f t="shared" si="19"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="81" spans="3:16" x14ac:dyDescent="0.25">
@@ -36923,7 +36924,7 @@
       </c>
       <c r="F81">
         <f t="shared" si="17"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="H81">
         <v>80000</v>
@@ -36937,7 +36938,7 @@
       </c>
       <c r="K81">
         <f t="shared" si="15"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M81">
         <v>40000</v>
@@ -36951,7 +36952,7 @@
       </c>
       <c r="P81">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="82" spans="3:16" x14ac:dyDescent="0.25">
@@ -36967,7 +36968,7 @@
       </c>
       <c r="F82">
         <f t="shared" si="17"/>
-        <v>5.4700000000000013E-2</v>
+        <v>6.0853750000000005E-2</v>
       </c>
       <c r="H82">
         <v>81000</v>
@@ -36981,7 +36982,7 @@
       </c>
       <c r="K82">
         <f>I82*($A$5/360)</f>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M82">
         <v>40500</v>
@@ -36995,7 +36996,7 @@
       </c>
       <c r="P82">
         <f t="shared" si="19"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="83" spans="3:16" x14ac:dyDescent="0.25">
@@ -37011,7 +37012,7 @@
       </c>
       <c r="F83">
         <f t="shared" si="17"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="H83">
         <v>82000</v>
@@ -37025,7 +37026,7 @@
       </c>
       <c r="K83">
         <f t="shared" ref="K83:K100" si="23">I83*($A$5/360)</f>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
       <c r="M83">
         <v>41000</v>
@@ -37039,7 +37040,7 @@
       </c>
       <c r="P83">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="84" spans="3:16" x14ac:dyDescent="0.25">
@@ -37055,7 +37056,7 @@
       </c>
       <c r="F84">
         <f t="shared" si="17"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="H84">
         <v>83000</v>
@@ -37069,7 +37070,7 @@
       </c>
       <c r="K84">
         <f t="shared" si="23"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M84">
         <v>41500</v>
@@ -37083,7 +37084,7 @@
       </c>
       <c r="P84">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="85" spans="3:16" x14ac:dyDescent="0.25">
@@ -37099,7 +37100,7 @@
       </c>
       <c r="F85">
         <f t="shared" si="17"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
       <c r="H85">
         <v>84000</v>
@@ -37113,7 +37114,7 @@
       </c>
       <c r="K85">
         <f t="shared" si="23"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
       <c r="M85">
         <v>42000</v>
@@ -37127,7 +37128,7 @@
       </c>
       <c r="P85">
         <f t="shared" si="19"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="86" spans="3:16" x14ac:dyDescent="0.25">
@@ -37143,7 +37144,7 @@
       </c>
       <c r="F86">
         <f t="shared" si="17"/>
-        <v>6.4433333333333342E-2</v>
+        <v>7.1682083333333327E-2</v>
       </c>
       <c r="H86">
         <v>85000</v>
@@ -37157,7 +37158,7 @@
       </c>
       <c r="K86">
         <f t="shared" si="23"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M86">
         <v>42500</v>
@@ -37171,7 +37172,7 @@
       </c>
       <c r="P86">
         <f t="shared" si="19"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="87" spans="3:16" x14ac:dyDescent="0.25">
@@ -37187,7 +37188,7 @@
       </c>
       <c r="F87">
         <f t="shared" si="17"/>
-        <v>6.4433333333333342E-2</v>
+        <v>7.1682083333333327E-2</v>
       </c>
       <c r="H87">
         <v>86000</v>
@@ -37201,7 +37202,7 @@
       </c>
       <c r="K87">
         <f t="shared" si="23"/>
-        <v>5.2400000000000009E-2</v>
+        <v>5.8295000000000007E-2</v>
       </c>
       <c r="M87">
         <v>43000</v>
@@ -37215,7 +37216,7 @@
       </c>
       <c r="P87">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="88" spans="3:16" x14ac:dyDescent="0.25">
@@ -37231,7 +37232,7 @@
       </c>
       <c r="F88">
         <f t="shared" si="17"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="H88">
         <v>87000</v>
@@ -37245,7 +37246,7 @@
       </c>
       <c r="K88">
         <f t="shared" si="23"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
       <c r="M88">
         <v>43500</v>
@@ -37259,7 +37260,7 @@
       </c>
       <c r="P88">
         <f t="shared" si="19"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="89" spans="3:16" x14ac:dyDescent="0.25">
@@ -37275,7 +37276,7 @@
       </c>
       <c r="F89">
         <f t="shared" si="17"/>
-        <v>5.0100000000000006E-2</v>
+        <v>5.5736250000000001E-2</v>
       </c>
       <c r="H89">
         <v>88000</v>
@@ -37289,7 +37290,7 @@
       </c>
       <c r="K89">
         <f t="shared" si="23"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M89">
         <v>44000</v>
@@ -37303,7 +37304,7 @@
       </c>
       <c r="P89">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="90" spans="3:16" x14ac:dyDescent="0.25">
@@ -37319,7 +37320,7 @@
       </c>
       <c r="F90">
         <f t="shared" si="17"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
       <c r="H90">
         <v>89000</v>
@@ -37333,7 +37334,7 @@
       </c>
       <c r="K90">
         <f t="shared" si="23"/>
-        <v>6.2633333333333346E-2</v>
+        <v>6.9679583333333336E-2</v>
       </c>
       <c r="M90">
         <v>44500</v>
@@ -37347,7 +37348,7 @@
       </c>
       <c r="P90">
         <f t="shared" si="19"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="91" spans="3:16" x14ac:dyDescent="0.25">
@@ -37363,7 +37364,7 @@
       </c>
       <c r="F91">
         <f t="shared" si="17"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="H91">
         <v>90000</v>
@@ -37377,7 +37378,7 @@
       </c>
       <c r="K91">
         <f t="shared" si="23"/>
-        <v>6.2633333333333346E-2</v>
+        <v>6.9679583333333336E-2</v>
       </c>
       <c r="M91">
         <v>45000</v>
@@ -37391,7 +37392,7 @@
       </c>
       <c r="P91">
         <f t="shared" si="19"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="92" spans="3:16" x14ac:dyDescent="0.25">
@@ -37407,7 +37408,7 @@
       </c>
       <c r="F92">
         <f t="shared" si="17"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="H92">
         <v>91000</v>
@@ -37421,7 +37422,7 @@
       </c>
       <c r="K92">
         <f t="shared" si="23"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M92">
         <v>45500</v>
@@ -37435,7 +37436,7 @@
       </c>
       <c r="P92">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="93" spans="3:16" x14ac:dyDescent="0.25">
@@ -37451,7 +37452,7 @@
       </c>
       <c r="F93">
         <f t="shared" si="17"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
       <c r="H93">
         <v>92000</v>
@@ -37465,7 +37466,7 @@
       </c>
       <c r="K93">
         <f t="shared" si="23"/>
-        <v>6.0066666666666678E-2</v>
+        <v>6.6824166666666671E-2</v>
       </c>
       <c r="M93">
         <v>46000</v>
@@ -37479,7 +37480,7 @@
       </c>
       <c r="P93">
         <f t="shared" si="19"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="94" spans="3:16" x14ac:dyDescent="0.25">
@@ -37495,7 +37496,7 @@
       </c>
       <c r="F94">
         <f t="shared" si="17"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="H94">
         <v>93000</v>
@@ -37509,7 +37510,7 @@
       </c>
       <c r="K94">
         <f t="shared" si="23"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M94">
         <v>46500</v>
@@ -37523,7 +37524,7 @@
       </c>
       <c r="P94">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="95" spans="3:16" x14ac:dyDescent="0.25">
@@ -37539,7 +37540,7 @@
       </c>
       <c r="F95">
         <f t="shared" si="17"/>
-        <v>6.5966666666666673E-2</v>
+        <v>7.3387916666666664E-2</v>
       </c>
       <c r="H95">
         <v>94000</v>
@@ -37553,7 +37554,7 @@
       </c>
       <c r="K95">
         <f t="shared" si="23"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M95">
         <v>47000</v>
@@ -37567,7 +37568,7 @@
       </c>
       <c r="P95">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="96" spans="3:16" x14ac:dyDescent="0.25">
@@ -37583,7 +37584,7 @@
       </c>
       <c r="F96">
         <f t="shared" si="17"/>
-        <v>6.7000000000000018E-2</v>
+        <v>7.4537500000000007E-2</v>
       </c>
       <c r="H96">
         <v>95000</v>
@@ -37597,7 +37598,7 @@
       </c>
       <c r="K96">
         <f t="shared" si="23"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="M96">
         <v>47500</v>
@@ -37611,7 +37612,7 @@
       </c>
       <c r="P96">
         <f t="shared" si="19"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="97" spans="3:16" x14ac:dyDescent="0.25">
@@ -37627,7 +37628,7 @@
       </c>
       <c r="F97">
         <f t="shared" si="17"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
       <c r="H97">
         <v>96000</v>
@@ -37641,7 +37642,7 @@
       </c>
       <c r="K97">
         <f t="shared" si="23"/>
-        <v>5.7533333333333353E-2</v>
+        <v>6.4005833333333345E-2</v>
       </c>
       <c r="M97">
         <v>48000</v>
@@ -37655,7 +37656,7 @@
       </c>
       <c r="P97">
         <f t="shared" si="19"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="98" spans="3:16" x14ac:dyDescent="0.25">
@@ -37671,7 +37672,7 @@
       </c>
       <c r="F98">
         <f t="shared" si="17"/>
-        <v>4.9100000000000012E-2</v>
+        <v>5.4623750000000006E-2</v>
       </c>
       <c r="H98">
         <v>97000</v>
@@ -37685,7 +37686,7 @@
       </c>
       <c r="K98">
         <f t="shared" si="23"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="M98">
         <v>48500</v>
@@ -37699,7 +37700,7 @@
       </c>
       <c r="P98">
         <f t="shared" si="19"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="99" spans="3:16" x14ac:dyDescent="0.25">
@@ -37715,7 +37716,7 @@
       </c>
       <c r="F99">
         <f t="shared" si="17"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
       <c r="H99">
         <v>98000</v>
@@ -37729,7 +37730,7 @@
       </c>
       <c r="K99">
         <f t="shared" si="23"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M99">
         <v>49000</v>
@@ -37743,7 +37744,7 @@
       </c>
       <c r="P99">
         <f t="shared" si="19"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="100" spans="3:16" x14ac:dyDescent="0.25">
@@ -37759,7 +37760,7 @@
       </c>
       <c r="F100">
         <f t="shared" si="17"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="H100">
         <v>99000</v>
@@ -37773,7 +37774,7 @@
       </c>
       <c r="K100">
         <f t="shared" si="23"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="M100">
         <v>49500</v>
@@ -37787,7 +37788,7 @@
       </c>
       <c r="P100">
         <f t="shared" si="19"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="101" spans="3:16" x14ac:dyDescent="0.25">
@@ -37803,7 +37804,7 @@
       </c>
       <c r="F101">
         <f t="shared" si="17"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
     </row>
     <row r="102" spans="3:16" x14ac:dyDescent="0.25">
@@ -37819,15 +37820,15 @@
       </c>
       <c r="F102">
         <f t="shared" si="17"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="K102">
         <f>AVERAGE(K61:K100)</f>
-        <v>5.911750000000001E-2</v>
+        <v>6.576821875000001E-2</v>
       </c>
       <c r="P102">
         <f>AVERAGE(P81:P100)</f>
-        <v>5.3053333333333355E-2</v>
+        <v>5.9021833333333329E-2</v>
       </c>
     </row>
     <row r="103" spans="3:16" x14ac:dyDescent="0.25">
@@ -37843,15 +37844,15 @@
       </c>
       <c r="F103">
         <f t="shared" si="17"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="K103">
         <f>_xlfn.VAR.P(K61:K100)</f>
-        <v>1.3624721527777777E-5</v>
+        <v>1.6862721753363718E-5</v>
       </c>
       <c r="P103">
         <f>_xlfn.VAR.P(P81:P100)</f>
-        <v>3.1796000000000081E-6</v>
+        <v>3.935251812499998E-6</v>
       </c>
     </row>
     <row r="104" spans="3:16" x14ac:dyDescent="0.25">
@@ -37867,7 +37868,7 @@
       </c>
       <c r="F104">
         <f t="shared" si="17"/>
-        <v>6.4933333333333343E-2</v>
+        <v>7.2238333333333335E-2</v>
       </c>
     </row>
     <row r="105" spans="3:16" x14ac:dyDescent="0.25">
@@ -37883,7 +37884,7 @@
       </c>
       <c r="F105">
         <f t="shared" si="17"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
     </row>
     <row r="106" spans="3:16" x14ac:dyDescent="0.25">
@@ -37899,7 +37900,7 @@
       </c>
       <c r="F106">
         <f t="shared" si="17"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
     </row>
     <row r="107" spans="3:16" x14ac:dyDescent="0.25">
@@ -37915,7 +37916,7 @@
       </c>
       <c r="F107">
         <f t="shared" si="17"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
     </row>
     <row r="108" spans="3:16" x14ac:dyDescent="0.25">
@@ -37931,7 +37932,7 @@
       </c>
       <c r="F108">
         <f t="shared" si="17"/>
-        <v>5.1633333333333344E-2</v>
+        <v>5.7442083333333338E-2</v>
       </c>
     </row>
     <row r="109" spans="3:16" x14ac:dyDescent="0.25">
@@ -37947,7 +37948,7 @@
       </c>
       <c r="F109">
         <f t="shared" si="17"/>
-        <v>5.0633333333333343E-2</v>
+        <v>5.6329583333333336E-2</v>
       </c>
     </row>
     <row r="110" spans="3:16" x14ac:dyDescent="0.25">
@@ -37963,7 +37964,7 @@
       </c>
       <c r="F110">
         <f t="shared" si="17"/>
-        <v>5.3166666666666675E-2</v>
+        <v>5.9147916666666668E-2</v>
       </c>
     </row>
     <row r="111" spans="3:16" x14ac:dyDescent="0.25">
@@ -37979,7 +37980,7 @@
       </c>
       <c r="F111">
         <f t="shared" si="17"/>
-        <v>5.7266666666666674E-2</v>
+        <v>6.3709166666666664E-2</v>
       </c>
     </row>
     <row r="112" spans="3:16" x14ac:dyDescent="0.25">
@@ -37995,7 +37996,7 @@
       </c>
       <c r="F112">
         <f t="shared" si="17"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
     </row>
     <row r="113" spans="3:6" x14ac:dyDescent="0.25">
@@ -38011,7 +38012,7 @@
       </c>
       <c r="F113">
         <f t="shared" si="17"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
     </row>
     <row r="114" spans="3:6" x14ac:dyDescent="0.25">
@@ -38027,7 +38028,7 @@
       </c>
       <c r="F114">
         <f t="shared" si="17"/>
-        <v>7.5666666666666674E-2</v>
+        <v>8.4179166666666666E-2</v>
       </c>
     </row>
     <row r="115" spans="3:6" x14ac:dyDescent="0.25">
@@ -38043,7 +38044,7 @@
       </c>
       <c r="F115">
         <f t="shared" si="17"/>
-        <v>7.1600000000000011E-2</v>
+        <v>7.9655000000000004E-2</v>
       </c>
     </row>
     <row r="116" spans="3:6" x14ac:dyDescent="0.25">
@@ -38059,7 +38060,7 @@
       </c>
       <c r="F116">
         <f t="shared" si="17"/>
-        <v>7.006666666666668E-2</v>
+        <v>7.7949166666666667E-2</v>
       </c>
     </row>
     <row r="117" spans="3:6" x14ac:dyDescent="0.25">
@@ -38075,7 +38076,7 @@
       </c>
       <c r="F117">
         <f t="shared" si="17"/>
-        <v>7.006666666666668E-2</v>
+        <v>7.7949166666666667E-2</v>
       </c>
     </row>
     <row r="118" spans="3:6" x14ac:dyDescent="0.25">
@@ -38091,7 +38092,7 @@
       </c>
       <c r="F118">
         <f t="shared" si="17"/>
-        <v>6.7000000000000018E-2</v>
+        <v>7.4537500000000007E-2</v>
       </c>
     </row>
     <row r="119" spans="3:6" x14ac:dyDescent="0.25">
@@ -38107,7 +38108,7 @@
       </c>
       <c r="F119">
         <f t="shared" si="17"/>
-        <v>5.9300000000000005E-2</v>
+        <v>6.5971249999999995E-2</v>
       </c>
     </row>
     <row r="120" spans="3:6" x14ac:dyDescent="0.25">
@@ -38123,7 +38124,7 @@
       </c>
       <c r="F120">
         <f t="shared" si="17"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
     </row>
     <row r="121" spans="3:6" x14ac:dyDescent="0.25">
@@ -38139,7 +38140,7 @@
       </c>
       <c r="F121">
         <f t="shared" si="17"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
     </row>
     <row r="122" spans="3:6" x14ac:dyDescent="0.25">
@@ -38155,7 +38156,7 @@
       </c>
       <c r="F122">
         <f t="shared" si="17"/>
-        <v>7.006666666666668E-2</v>
+        <v>7.7949166666666667E-2</v>
       </c>
     </row>
     <row r="123" spans="3:6" x14ac:dyDescent="0.25">
@@ -38171,7 +38172,7 @@
       </c>
       <c r="F123">
         <f t="shared" si="17"/>
-        <v>7.1066666666666681E-2</v>
+        <v>7.9061666666666669E-2</v>
       </c>
     </row>
     <row r="124" spans="3:6" x14ac:dyDescent="0.25">
@@ -38187,7 +38188,7 @@
       </c>
       <c r="F124">
         <f t="shared" si="17"/>
-        <v>6.953333333333335E-2</v>
+        <v>7.7355833333333332E-2</v>
       </c>
     </row>
     <row r="125" spans="3:6" x14ac:dyDescent="0.25">
@@ -38203,7 +38204,7 @@
       </c>
       <c r="F125">
         <f t="shared" si="17"/>
-        <v>7.5166666666666687E-2</v>
+        <v>8.3622916666666672E-2</v>
       </c>
     </row>
     <row r="126" spans="3:6" x14ac:dyDescent="0.25">
@@ -38219,7 +38220,7 @@
       </c>
       <c r="F126">
         <f t="shared" si="17"/>
-        <v>7.3633333333333342E-2</v>
+        <v>8.1917083333333335E-2</v>
       </c>
     </row>
     <row r="127" spans="3:6" x14ac:dyDescent="0.25">
@@ -38235,7 +38236,7 @@
       </c>
       <c r="F127">
         <f t="shared" si="17"/>
-        <v>6.4433333333333342E-2</v>
+        <v>7.1682083333333327E-2</v>
       </c>
     </row>
     <row r="128" spans="3:6" x14ac:dyDescent="0.25">
@@ -38251,7 +38252,7 @@
       </c>
       <c r="F128">
         <f t="shared" si="17"/>
-        <v>6.5966666666666673E-2</v>
+        <v>7.3387916666666664E-2</v>
       </c>
     </row>
     <row r="129" spans="3:14" x14ac:dyDescent="0.25">
@@ -38267,7 +38268,7 @@
       </c>
       <c r="F129">
         <f t="shared" si="17"/>
-        <v>6.4433333333333342E-2</v>
+        <v>7.1682083333333327E-2</v>
       </c>
     </row>
     <row r="130" spans="3:14" x14ac:dyDescent="0.25">
@@ -38283,7 +38284,7 @@
       </c>
       <c r="F130">
         <f t="shared" si="17"/>
-        <v>6.8000000000000005E-2</v>
+        <v>7.5649999999999995E-2</v>
       </c>
     </row>
     <row r="131" spans="3:14" x14ac:dyDescent="0.25">
@@ -38299,7 +38300,7 @@
       </c>
       <c r="F131">
         <f t="shared" ref="F131:F194" si="25">D131*($A$5/360)</f>
-        <v>7.2100000000000011E-2</v>
+        <v>8.0211249999999998E-2</v>
       </c>
     </row>
     <row r="132" spans="3:14" x14ac:dyDescent="0.25">
@@ -38315,7 +38316,7 @@
       </c>
       <c r="F132">
         <f t="shared" si="25"/>
-        <v>7.1066666666666681E-2</v>
+        <v>7.9061666666666669E-2</v>
       </c>
     </row>
     <row r="133" spans="3:14" x14ac:dyDescent="0.25">
@@ -38331,7 +38332,7 @@
       </c>
       <c r="F133">
         <f t="shared" si="25"/>
-        <v>6.8000000000000005E-2</v>
+        <v>7.5649999999999995E-2</v>
       </c>
     </row>
     <row r="134" spans="3:14" x14ac:dyDescent="0.25">
@@ -38347,7 +38348,7 @@
       </c>
       <c r="F134">
         <f t="shared" si="25"/>
-        <v>6.953333333333335E-2</v>
+        <v>7.7355833333333332E-2</v>
       </c>
     </row>
     <row r="135" spans="3:14" x14ac:dyDescent="0.25">
@@ -38363,7 +38364,7 @@
       </c>
       <c r="F135">
         <f t="shared" si="25"/>
-        <v>7.1600000000000011E-2</v>
+        <v>7.9655000000000004E-2</v>
       </c>
     </row>
     <row r="136" spans="3:14" x14ac:dyDescent="0.25">
@@ -38379,7 +38380,7 @@
       </c>
       <c r="F136">
         <f t="shared" si="25"/>
-        <v>7.056666666666668E-2</v>
+        <v>7.8505416666666675E-2</v>
       </c>
       <c r="K136" t="s">
         <v>16</v>
@@ -38398,7 +38399,7 @@
       </c>
       <c r="F137">
         <f t="shared" si="25"/>
-        <v>7.2100000000000011E-2</v>
+        <v>8.0211249999999998E-2</v>
       </c>
       <c r="K137" t="s">
         <v>12</v>
@@ -38423,7 +38424,7 @@
       </c>
       <c r="F138">
         <f t="shared" si="25"/>
-        <v>6.5433333333333343E-2</v>
+        <v>7.2794583333333329E-2</v>
       </c>
       <c r="K138">
         <f>L138*(60/(2*PI()))</f>
@@ -38451,7 +38452,7 @@
       </c>
       <c r="F139">
         <f t="shared" si="25"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="K139" t="s">
         <v>11</v>
@@ -38470,7 +38471,7 @@
       </c>
       <c r="F140">
         <f t="shared" si="25"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
       <c r="K140" t="s">
         <v>12</v>
@@ -38492,7 +38493,7 @@
       </c>
       <c r="F141">
         <f t="shared" si="25"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
       <c r="K141">
         <v>181.68</v>
@@ -38515,7 +38516,7 @@
       </c>
       <c r="F142">
         <f t="shared" si="25"/>
-        <v>6.8000000000000005E-2</v>
+        <v>7.5649999999999995E-2</v>
       </c>
     </row>
     <row r="143" spans="3:14" x14ac:dyDescent="0.25">
@@ -38531,7 +38532,7 @@
       </c>
       <c r="F143">
         <f t="shared" si="25"/>
-        <v>6.3400000000000012E-2</v>
+        <v>7.0532499999999998E-2</v>
       </c>
     </row>
     <row r="144" spans="3:14" x14ac:dyDescent="0.25">
@@ -38547,7 +38548,7 @@
       </c>
       <c r="F144">
         <f t="shared" si="25"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
     </row>
     <row r="145" spans="3:20" x14ac:dyDescent="0.25">
@@ -38563,7 +38564,7 @@
       </c>
       <c r="F145">
         <f t="shared" si="25"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
     </row>
     <row r="146" spans="3:20" x14ac:dyDescent="0.25">
@@ -38579,7 +38580,7 @@
       </c>
       <c r="F146">
         <f t="shared" si="25"/>
-        <v>5.7266666666666674E-2</v>
+        <v>6.3709166666666664E-2</v>
       </c>
     </row>
     <row r="147" spans="3:20" x14ac:dyDescent="0.25">
@@ -38595,7 +38596,7 @@
       </c>
       <c r="F147">
         <f t="shared" si="25"/>
-        <v>5.3166666666666675E-2</v>
+        <v>5.9147916666666668E-2</v>
       </c>
     </row>
     <row r="148" spans="3:20" x14ac:dyDescent="0.25">
@@ -38611,7 +38612,7 @@
       </c>
       <c r="F148">
         <f t="shared" si="25"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="149" spans="3:20" x14ac:dyDescent="0.25">
@@ -38627,7 +38628,7 @@
       </c>
       <c r="F149">
         <f t="shared" si="25"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
     </row>
     <row r="150" spans="3:20" x14ac:dyDescent="0.25">
@@ -38643,7 +38644,7 @@
       </c>
       <c r="F150">
         <f t="shared" si="25"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="P150">
         <v>2.5000000000000001E-3</v>
@@ -38671,7 +38672,7 @@
       </c>
       <c r="F151">
         <f t="shared" si="25"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
       <c r="P151">
         <v>5.0000000000000001E-3</v>
@@ -38699,7 +38700,7 @@
       </c>
       <c r="F152">
         <f t="shared" si="25"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
       <c r="P152">
         <v>7.4999999999999997E-3</v>
@@ -38728,7 +38729,7 @@
       </c>
       <c r="F153">
         <f t="shared" si="25"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
       <c r="P153">
         <v>0.01</v>
@@ -38757,7 +38758,7 @@
       </c>
       <c r="F154">
         <f t="shared" si="25"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="P154">
         <v>1.2499999999999999E-2</v>
@@ -38786,7 +38787,7 @@
       </c>
       <c r="F155">
         <f t="shared" si="25"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="P155">
         <v>1.4999999999999999E-2</v>
@@ -38815,7 +38816,7 @@
       </c>
       <c r="F156">
         <f t="shared" si="25"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="P156">
         <v>1.7499999999999998E-2</v>
@@ -38844,7 +38845,7 @@
       </c>
       <c r="F157">
         <f t="shared" si="25"/>
-        <v>5.4700000000000013E-2</v>
+        <v>6.0853750000000005E-2</v>
       </c>
       <c r="P157">
         <v>0.02</v>
@@ -38873,7 +38874,7 @@
       </c>
       <c r="F158">
         <f t="shared" si="25"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="P158">
         <v>2.2499999999999999E-2</v>
@@ -38902,7 +38903,7 @@
       </c>
       <c r="F159">
         <f t="shared" si="25"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
       <c r="P159">
         <v>2.4999999999999998E-2</v>
@@ -38931,7 +38932,7 @@
       </c>
       <c r="F160">
         <f t="shared" si="25"/>
-        <v>5.3166666666666675E-2</v>
+        <v>5.9147916666666668E-2</v>
       </c>
       <c r="P160">
         <v>2.75E-2</v>
@@ -38960,7 +38961,7 @@
       </c>
       <c r="F161">
         <f t="shared" si="25"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
       <c r="P161">
         <v>0.03</v>
@@ -38989,7 +38990,7 @@
       </c>
       <c r="F162">
         <f t="shared" si="25"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
       <c r="P162">
         <v>3.2500000000000001E-2</v>
@@ -39018,7 +39019,7 @@
       </c>
       <c r="F163">
         <f t="shared" si="25"/>
-        <v>5.5233333333333343E-2</v>
+        <v>6.144708333333334E-2</v>
       </c>
       <c r="P163">
         <v>3.4999999999999996E-2</v>
@@ -39047,7 +39048,7 @@
       </c>
       <c r="F164">
         <f t="shared" si="25"/>
-        <v>5.3166666666666675E-2</v>
+        <v>5.9147916666666668E-2</v>
       </c>
       <c r="P164">
         <v>3.7499999999999999E-2</v>
@@ -39076,7 +39077,7 @@
       </c>
       <c r="F165">
         <f t="shared" si="25"/>
-        <v>4.6533333333333343E-2</v>
+        <v>5.176833333333334E-2</v>
       </c>
       <c r="P165">
         <v>0.04</v>
@@ -39105,7 +39106,7 @@
       </c>
       <c r="F166">
         <f t="shared" si="25"/>
-        <v>5.1633333333333344E-2</v>
+        <v>5.7442083333333338E-2</v>
       </c>
       <c r="P166">
         <v>4.2499999999999996E-2</v>
@@ -39134,7 +39135,7 @@
       </c>
       <c r="F167">
         <f t="shared" si="25"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="P167">
         <v>4.4999999999999998E-2</v>
@@ -39163,7 +39164,7 @@
       </c>
       <c r="F168">
         <f t="shared" si="25"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
       <c r="P168">
         <v>4.7500000000000001E-2</v>
@@ -39192,7 +39193,7 @@
       </c>
       <c r="F169">
         <f t="shared" si="25"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
       <c r="P169">
         <v>4.9999999999999996E-2</v>
@@ -39221,7 +39222,7 @@
       </c>
       <c r="F170">
         <f t="shared" si="25"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="P170">
         <v>5.2499999999999998E-2</v>
@@ -39250,7 +39251,7 @@
       </c>
       <c r="F171">
         <f t="shared" si="25"/>
-        <v>5.5233333333333343E-2</v>
+        <v>6.144708333333334E-2</v>
       </c>
       <c r="P171">
         <v>5.5E-2</v>
@@ -39279,7 +39280,7 @@
       </c>
       <c r="F172">
         <f t="shared" si="25"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
       <c r="P172">
         <v>5.7499999999999996E-2</v>
@@ -39308,7 +39309,7 @@
       </c>
       <c r="F173">
         <f t="shared" si="25"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
       <c r="P173">
         <v>0.06</v>
@@ -39337,7 +39338,7 @@
       </c>
       <c r="F174">
         <f t="shared" si="25"/>
-        <v>5.4700000000000013E-2</v>
+        <v>6.0853750000000005E-2</v>
       </c>
       <c r="P174">
         <v>6.25E-2</v>
@@ -39366,7 +39367,7 @@
       </c>
       <c r="F175">
         <f t="shared" si="25"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
       <c r="P175">
         <v>6.5000000000000002E-2</v>
@@ -39395,7 +39396,7 @@
       </c>
       <c r="F176">
         <f t="shared" si="25"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="P176">
         <v>6.7499999999999991E-2</v>
@@ -39424,7 +39425,7 @@
       </c>
       <c r="F177">
         <f t="shared" si="25"/>
-        <v>5.9300000000000005E-2</v>
+        <v>6.5971249999999995E-2</v>
       </c>
       <c r="P177">
         <v>6.9999999999999993E-2</v>
@@ -39453,7 +39454,7 @@
       </c>
       <c r="F178">
         <f t="shared" si="25"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
       <c r="P178">
         <v>7.2499999999999995E-2</v>
@@ -39482,7 +39483,7 @@
       </c>
       <c r="F179">
         <f t="shared" si="25"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="P179">
         <v>7.4999999999999997E-2</v>
@@ -39511,7 +39512,7 @@
       </c>
       <c r="F180">
         <f t="shared" si="25"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
       <c r="P180">
         <v>7.7499999999999999E-2</v>
@@ -39540,7 +39541,7 @@
       </c>
       <c r="F181">
         <f t="shared" si="25"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
       <c r="P181">
         <v>0.08</v>
@@ -39569,7 +39570,7 @@
       </c>
       <c r="F182">
         <f t="shared" si="25"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="P182">
         <v>8.249999999999999E-2</v>
@@ -39598,7 +39599,7 @@
       </c>
       <c r="F183">
         <f t="shared" si="25"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
       <c r="P183">
         <v>8.4999999999999992E-2</v>
@@ -39627,7 +39628,7 @@
       </c>
       <c r="F184">
         <f t="shared" si="25"/>
-        <v>5.2166666666666681E-2</v>
+        <v>5.8035416666666673E-2</v>
       </c>
       <c r="P184">
         <v>8.7499999999999994E-2</v>
@@ -39656,7 +39657,7 @@
       </c>
       <c r="F185">
         <f t="shared" si="25"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
       <c r="P185">
         <v>0.09</v>
@@ -39685,7 +39686,7 @@
       </c>
       <c r="F186">
         <f t="shared" si="25"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
       <c r="P186">
         <v>9.2499999999999999E-2</v>
@@ -39714,7 +39715,7 @@
       </c>
       <c r="F187">
         <f t="shared" si="25"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
       <c r="P187">
         <v>9.5000000000000001E-2</v>
@@ -39743,7 +39744,7 @@
       </c>
       <c r="F188">
         <f t="shared" si="25"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="P188">
         <v>9.7499999999999989E-2</v>
@@ -39772,7 +39773,7 @@
       </c>
       <c r="F189">
         <f t="shared" si="25"/>
-        <v>5.9300000000000005E-2</v>
+        <v>6.5971249999999995E-2</v>
       </c>
       <c r="P189">
         <v>9.9999999999999992E-2</v>
@@ -39801,7 +39802,7 @@
       </c>
       <c r="F190">
         <f t="shared" si="25"/>
-        <v>5.7266666666666674E-2</v>
+        <v>6.3709166666666664E-2</v>
       </c>
       <c r="P190">
         <v>0.10249999999999999</v>
@@ -39830,7 +39831,7 @@
       </c>
       <c r="F191">
         <f t="shared" si="25"/>
-        <v>5.4700000000000013E-2</v>
+        <v>6.0853750000000005E-2</v>
       </c>
       <c r="P191">
         <v>0.105</v>
@@ -39859,7 +39860,7 @@
       </c>
       <c r="F192">
         <f t="shared" si="25"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
       <c r="P192">
         <v>0.1075</v>
@@ -39888,7 +39889,7 @@
       </c>
       <c r="F193">
         <f t="shared" si="25"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
       <c r="P193">
         <v>0.11</v>
@@ -39917,7 +39918,7 @@
       </c>
       <c r="F194">
         <f t="shared" si="25"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
       <c r="P194">
         <v>0.11249999999999999</v>
@@ -39946,7 +39947,7 @@
       </c>
       <c r="F195">
         <f t="shared" ref="F195:F258" si="28">D195*($A$5/360)</f>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="P195">
         <v>0.11499999999999999</v>
@@ -39975,7 +39976,7 @@
       </c>
       <c r="F196">
         <f t="shared" si="28"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
       <c r="P196">
         <v>0.11749999999999999</v>
@@ -40004,7 +40005,7 @@
       </c>
       <c r="F197">
         <f t="shared" si="28"/>
-        <v>6.3400000000000012E-2</v>
+        <v>7.0532499999999998E-2</v>
       </c>
       <c r="P197">
         <v>0.12</v>
@@ -40033,7 +40034,7 @@
       </c>
       <c r="F198">
         <f t="shared" si="28"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
       <c r="P198">
         <v>0.1225</v>
@@ -40062,7 +40063,7 @@
       </c>
       <c r="F199">
         <f t="shared" si="28"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
       <c r="P199">
         <v>0.125</v>
@@ -40091,7 +40092,7 @@
       </c>
       <c r="F200">
         <f t="shared" si="28"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="P200">
         <v>0.1275</v>
@@ -40120,7 +40121,7 @@
       </c>
       <c r="F201">
         <f t="shared" si="28"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
       <c r="P201">
         <v>0.13</v>
@@ -40149,7 +40150,7 @@
       </c>
       <c r="F202">
         <f t="shared" si="28"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
       <c r="P202">
         <v>0.13250000000000001</v>
@@ -40178,7 +40179,7 @@
       </c>
       <c r="F203">
         <f t="shared" si="28"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
       <c r="P203">
         <v>0.13499999999999998</v>
@@ -40207,7 +40208,7 @@
       </c>
       <c r="F204">
         <f t="shared" si="28"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
       <c r="P204">
         <v>0.13749999999999998</v>
@@ -40236,7 +40237,7 @@
       </c>
       <c r="F205">
         <f t="shared" si="28"/>
-        <v>6.3400000000000012E-2</v>
+        <v>7.0532499999999998E-2</v>
       </c>
       <c r="P205">
         <v>0.13999999999999999</v>
@@ -40265,7 +40266,7 @@
       </c>
       <c r="F206">
         <f t="shared" si="28"/>
-        <v>7.2100000000000011E-2</v>
+        <v>8.0211249999999998E-2</v>
       </c>
       <c r="P206">
         <v>0.14249999999999999</v>
@@ -40294,7 +40295,7 @@
       </c>
       <c r="F207">
         <f t="shared" si="28"/>
-        <v>6.7500000000000018E-2</v>
+        <v>7.5093750000000001E-2</v>
       </c>
       <c r="P207">
         <v>0.14499999999999999</v>
@@ -40323,7 +40324,7 @@
       </c>
       <c r="F208">
         <f t="shared" si="28"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="P208">
         <v>0.14749999999999999</v>
@@ -40352,7 +40353,7 @@
       </c>
       <c r="F209">
         <f t="shared" si="28"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
       <c r="P209">
         <v>0.15</v>
@@ -40381,7 +40382,7 @@
       </c>
       <c r="F210">
         <f t="shared" si="28"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
     </row>
     <row r="211" spans="3:20" x14ac:dyDescent="0.25">
@@ -40397,7 +40398,7 @@
       </c>
       <c r="F211">
         <f t="shared" si="28"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
     </row>
     <row r="212" spans="3:20" x14ac:dyDescent="0.25">
@@ -40413,7 +40414,7 @@
       </c>
       <c r="F212">
         <f t="shared" si="28"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
     </row>
     <row r="213" spans="3:20" x14ac:dyDescent="0.25">
@@ -40429,7 +40430,7 @@
       </c>
       <c r="F213">
         <f t="shared" si="28"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
     </row>
     <row r="214" spans="3:20" x14ac:dyDescent="0.25">
@@ -40445,7 +40446,7 @@
       </c>
       <c r="F214">
         <f t="shared" si="28"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
     </row>
     <row r="215" spans="3:20" x14ac:dyDescent="0.25">
@@ -40461,7 +40462,7 @@
       </c>
       <c r="F215">
         <f t="shared" si="28"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
     </row>
     <row r="216" spans="3:20" x14ac:dyDescent="0.25">
@@ -40477,7 +40478,7 @@
       </c>
       <c r="F216">
         <f t="shared" si="28"/>
-        <v>6.3400000000000012E-2</v>
+        <v>7.0532499999999998E-2</v>
       </c>
     </row>
     <row r="217" spans="3:20" x14ac:dyDescent="0.25">
@@ -40493,7 +40494,7 @@
       </c>
       <c r="F217">
         <f t="shared" si="28"/>
-        <v>6.1866666666666674E-2</v>
+        <v>6.8826666666666661E-2</v>
       </c>
     </row>
     <row r="218" spans="3:20" x14ac:dyDescent="0.25">
@@ -40509,7 +40510,7 @@
       </c>
       <c r="F218">
         <f t="shared" si="28"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
     </row>
     <row r="219" spans="3:20" x14ac:dyDescent="0.25">
@@ -40525,7 +40526,7 @@
       </c>
       <c r="F219">
         <f t="shared" si="28"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="220" spans="3:20" x14ac:dyDescent="0.25">
@@ -40541,7 +40542,7 @@
       </c>
       <c r="F220">
         <f t="shared" si="28"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="221" spans="3:20" x14ac:dyDescent="0.25">
@@ -40557,7 +40558,7 @@
       </c>
       <c r="F221">
         <f t="shared" si="28"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
     </row>
     <row r="222" spans="3:20" x14ac:dyDescent="0.25">
@@ -40573,7 +40574,7 @@
       </c>
       <c r="F222">
         <f t="shared" si="28"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="223" spans="3:20" x14ac:dyDescent="0.25">
@@ -40589,7 +40590,7 @@
       </c>
       <c r="F223">
         <f t="shared" si="28"/>
-        <v>5.5233333333333343E-2</v>
+        <v>6.144708333333334E-2</v>
       </c>
     </row>
     <row r="224" spans="3:20" x14ac:dyDescent="0.25">
@@ -40605,7 +40606,7 @@
       </c>
       <c r="F224">
         <f t="shared" si="28"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="225" spans="3:6" x14ac:dyDescent="0.25">
@@ -40621,7 +40622,7 @@
       </c>
       <c r="F225">
         <f t="shared" si="28"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
     </row>
     <row r="226" spans="3:6" x14ac:dyDescent="0.25">
@@ -40637,7 +40638,7 @@
       </c>
       <c r="F226">
         <f t="shared" si="28"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
     </row>
     <row r="227" spans="3:6" x14ac:dyDescent="0.25">
@@ -40653,7 +40654,7 @@
       </c>
       <c r="F227">
         <f t="shared" si="28"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
     </row>
     <row r="228" spans="3:6" x14ac:dyDescent="0.25">
@@ -40669,7 +40670,7 @@
       </c>
       <c r="F228">
         <f t="shared" si="28"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
     </row>
     <row r="229" spans="3:6" x14ac:dyDescent="0.25">
@@ -40685,7 +40686,7 @@
       </c>
       <c r="F229">
         <f t="shared" si="28"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
     </row>
     <row r="230" spans="3:6" x14ac:dyDescent="0.25">
@@ -40701,7 +40702,7 @@
       </c>
       <c r="F230">
         <f t="shared" si="28"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
     </row>
     <row r="231" spans="3:6" x14ac:dyDescent="0.25">
@@ -40717,7 +40718,7 @@
       </c>
       <c r="F231">
         <f t="shared" si="28"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
     </row>
     <row r="232" spans="3:6" x14ac:dyDescent="0.25">
@@ -40733,7 +40734,7 @@
       </c>
       <c r="F232">
         <f t="shared" si="28"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
     </row>
     <row r="233" spans="3:6" x14ac:dyDescent="0.25">
@@ -40749,7 +40750,7 @@
       </c>
       <c r="F233">
         <f t="shared" si="28"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
     </row>
     <row r="234" spans="3:6" x14ac:dyDescent="0.25">
@@ -40765,7 +40766,7 @@
       </c>
       <c r="F234">
         <f t="shared" si="28"/>
-        <v>5.7266666666666674E-2</v>
+        <v>6.3709166666666664E-2</v>
       </c>
     </row>
     <row r="235" spans="3:6" x14ac:dyDescent="0.25">
@@ -40781,7 +40782,7 @@
       </c>
       <c r="F235">
         <f t="shared" si="28"/>
-        <v>6.3400000000000012E-2</v>
+        <v>7.0532499999999998E-2</v>
       </c>
     </row>
     <row r="236" spans="3:6" x14ac:dyDescent="0.25">
@@ -40797,7 +40798,7 @@
       </c>
       <c r="F236">
         <f t="shared" si="28"/>
-        <v>6.3400000000000012E-2</v>
+        <v>7.0532499999999998E-2</v>
       </c>
     </row>
     <row r="237" spans="3:6" x14ac:dyDescent="0.25">
@@ -40813,7 +40814,7 @@
       </c>
       <c r="F237">
         <f t="shared" si="28"/>
-        <v>5.9300000000000005E-2</v>
+        <v>6.5971249999999995E-2</v>
       </c>
     </row>
     <row r="238" spans="3:6" x14ac:dyDescent="0.25">
@@ -40829,7 +40830,7 @@
       </c>
       <c r="F238">
         <f t="shared" si="28"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
     </row>
     <row r="239" spans="3:6" x14ac:dyDescent="0.25">
@@ -40845,7 +40846,7 @@
       </c>
       <c r="F239">
         <f t="shared" si="28"/>
-        <v>5.3166666666666675E-2</v>
+        <v>5.9147916666666668E-2</v>
       </c>
     </row>
     <row r="240" spans="3:6" x14ac:dyDescent="0.25">
@@ -40861,7 +40862,7 @@
       </c>
       <c r="F240">
         <f t="shared" si="28"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
     </row>
     <row r="241" spans="3:6" x14ac:dyDescent="0.25">
@@ -40877,7 +40878,7 @@
       </c>
       <c r="F241">
         <f t="shared" si="28"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
     </row>
     <row r="242" spans="3:6" x14ac:dyDescent="0.25">
@@ -40893,7 +40894,7 @@
       </c>
       <c r="F242">
         <f t="shared" si="28"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
     </row>
     <row r="243" spans="3:6" x14ac:dyDescent="0.25">
@@ -40909,7 +40910,7 @@
       </c>
       <c r="F243">
         <f t="shared" si="28"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="244" spans="3:6" x14ac:dyDescent="0.25">
@@ -40925,7 +40926,7 @@
       </c>
       <c r="F244">
         <f t="shared" si="28"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
     </row>
     <row r="245" spans="3:6" x14ac:dyDescent="0.25">
@@ -40941,7 +40942,7 @@
       </c>
       <c r="F245">
         <f t="shared" si="28"/>
-        <v>6.4433333333333342E-2</v>
+        <v>7.1682083333333327E-2</v>
       </c>
     </row>
     <row r="246" spans="3:6" x14ac:dyDescent="0.25">
@@ -40957,7 +40958,7 @@
       </c>
       <c r="F246">
         <f t="shared" si="28"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="247" spans="3:6" x14ac:dyDescent="0.25">
@@ -40973,7 +40974,7 @@
       </c>
       <c r="F247">
         <f t="shared" si="28"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
     </row>
     <row r="248" spans="3:6" x14ac:dyDescent="0.25">
@@ -40989,7 +40990,7 @@
       </c>
       <c r="F248">
         <f t="shared" si="28"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
     </row>
     <row r="249" spans="3:6" x14ac:dyDescent="0.25">
@@ -41005,7 +41006,7 @@
       </c>
       <c r="F249">
         <f t="shared" si="28"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="250" spans="3:6" x14ac:dyDescent="0.25">
@@ -41021,7 +41022,7 @@
       </c>
       <c r="F250">
         <f t="shared" si="28"/>
-        <v>6.3400000000000012E-2</v>
+        <v>7.0532499999999998E-2</v>
       </c>
     </row>
     <row r="251" spans="3:6" x14ac:dyDescent="0.25">
@@ -41037,7 +41038,7 @@
       </c>
       <c r="F251">
         <f t="shared" si="28"/>
-        <v>6.136666666666668E-2</v>
+        <v>6.8270416666666667E-2</v>
       </c>
     </row>
     <row r="252" spans="3:6" x14ac:dyDescent="0.25">
@@ -41053,7 +41054,7 @@
       </c>
       <c r="F252">
         <f t="shared" si="28"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
     </row>
     <row r="253" spans="3:6" x14ac:dyDescent="0.25">
@@ -41069,7 +41070,7 @@
       </c>
       <c r="F253">
         <f t="shared" si="28"/>
-        <v>6.2900000000000011E-2</v>
+        <v>6.9976250000000004E-2</v>
       </c>
     </row>
     <row r="254" spans="3:6" x14ac:dyDescent="0.25">
@@ -41085,7 +41086,7 @@
       </c>
       <c r="F254">
         <f t="shared" si="28"/>
-        <v>6.5433333333333343E-2</v>
+        <v>7.2794583333333329E-2</v>
       </c>
     </row>
     <row r="255" spans="3:6" x14ac:dyDescent="0.25">
@@ -41101,7 +41102,7 @@
       </c>
       <c r="F255">
         <f t="shared" si="28"/>
-        <v>7.2100000000000011E-2</v>
+        <v>8.0211249999999998E-2</v>
       </c>
     </row>
     <row r="256" spans="3:6" x14ac:dyDescent="0.25">
@@ -41117,7 +41118,7 @@
       </c>
       <c r="F256">
         <f t="shared" si="28"/>
-        <v>7.2100000000000011E-2</v>
+        <v>8.0211249999999998E-2</v>
       </c>
     </row>
     <row r="257" spans="3:6" x14ac:dyDescent="0.25">
@@ -41133,7 +41134,7 @@
       </c>
       <c r="F257">
         <f t="shared" si="28"/>
-        <v>6.3400000000000012E-2</v>
+        <v>7.0532499999999998E-2</v>
       </c>
     </row>
     <row r="258" spans="3:6" x14ac:dyDescent="0.25">
@@ -41149,7 +41150,7 @@
       </c>
       <c r="F258">
         <f t="shared" si="28"/>
-        <v>6.5966666666666673E-2</v>
+        <v>7.3387916666666664E-2</v>
       </c>
     </row>
     <row r="259" spans="3:6" x14ac:dyDescent="0.25">
@@ -41165,7 +41166,7 @@
       </c>
       <c r="F259">
         <f t="shared" ref="F259:F320" si="30">D259*($A$5/360)</f>
-        <v>6.5966666666666673E-2</v>
+        <v>7.3387916666666664E-2</v>
       </c>
     </row>
     <row r="260" spans="3:6" x14ac:dyDescent="0.25">
@@ -41181,7 +41182,7 @@
       </c>
       <c r="F260">
         <f t="shared" si="30"/>
-        <v>7.1066666666666681E-2</v>
+        <v>7.9061666666666669E-2</v>
       </c>
     </row>
     <row r="261" spans="3:6" x14ac:dyDescent="0.25">
@@ -41197,7 +41198,7 @@
       </c>
       <c r="F261">
         <f t="shared" si="30"/>
-        <v>7.1066666666666681E-2</v>
+        <v>7.9061666666666669E-2</v>
       </c>
     </row>
     <row r="262" spans="3:6" x14ac:dyDescent="0.25">
@@ -41213,7 +41214,7 @@
       </c>
       <c r="F262">
         <f t="shared" si="30"/>
-        <v>6.7500000000000018E-2</v>
+        <v>7.5093750000000001E-2</v>
       </c>
     </row>
     <row r="263" spans="3:6" x14ac:dyDescent="0.25">
@@ -41229,7 +41230,7 @@
       </c>
       <c r="F263">
         <f t="shared" si="30"/>
-        <v>6.5466666666666687E-2</v>
+        <v>7.283166666666667E-2</v>
       </c>
     </row>
     <row r="264" spans="3:6" x14ac:dyDescent="0.25">
@@ -41245,7 +41246,7 @@
       </c>
       <c r="F264">
         <f t="shared" si="30"/>
-        <v>6.5966666666666673E-2</v>
+        <v>7.3387916666666664E-2</v>
       </c>
     </row>
     <row r="265" spans="3:6" x14ac:dyDescent="0.25">
@@ -41261,7 +41262,7 @@
       </c>
       <c r="F265">
         <f t="shared" si="30"/>
-        <v>7.3633333333333342E-2</v>
+        <v>8.1917083333333335E-2</v>
       </c>
     </row>
     <row r="266" spans="3:6" x14ac:dyDescent="0.25">
@@ -41277,7 +41278,7 @@
       </c>
       <c r="F266">
         <f t="shared" si="30"/>
-        <v>7.3133333333333356E-2</v>
+        <v>8.1360833333333341E-2</v>
       </c>
     </row>
     <row r="267" spans="3:6" x14ac:dyDescent="0.25">
@@ -41293,7 +41294,7 @@
       </c>
       <c r="F267">
         <f t="shared" si="30"/>
-        <v>6.953333333333335E-2</v>
+        <v>7.7355833333333332E-2</v>
       </c>
     </row>
     <row r="268" spans="3:6" x14ac:dyDescent="0.25">
@@ -41309,7 +41310,7 @@
       </c>
       <c r="F268">
         <f t="shared" si="30"/>
-        <v>7.1066666666666681E-2</v>
+        <v>7.9061666666666669E-2</v>
       </c>
     </row>
     <row r="269" spans="3:6" x14ac:dyDescent="0.25">
@@ -41325,7 +41326,7 @@
       </c>
       <c r="F269">
         <f t="shared" si="30"/>
-        <v>7.2600000000000012E-2</v>
+        <v>8.0767500000000006E-2</v>
       </c>
     </row>
     <row r="270" spans="3:6" x14ac:dyDescent="0.25">
@@ -41341,7 +41342,7 @@
       </c>
       <c r="F270">
         <f t="shared" si="30"/>
-        <v>7.6700000000000018E-2</v>
+        <v>8.5328750000000009E-2</v>
       </c>
     </row>
     <row r="271" spans="3:6" x14ac:dyDescent="0.25">
@@ -41357,7 +41358,7 @@
       </c>
       <c r="F271">
         <f t="shared" si="30"/>
-        <v>7.5166666666666687E-2</v>
+        <v>8.3622916666666672E-2</v>
       </c>
     </row>
     <row r="272" spans="3:6" x14ac:dyDescent="0.25">
@@ -41373,7 +41374,7 @@
       </c>
       <c r="F272">
         <f t="shared" si="30"/>
-        <v>7.2100000000000011E-2</v>
+        <v>8.0211249999999998E-2</v>
       </c>
     </row>
     <row r="273" spans="3:6" x14ac:dyDescent="0.25">
@@ -41389,7 +41390,7 @@
       </c>
       <c r="F273">
         <f t="shared" si="30"/>
-        <v>6.7000000000000018E-2</v>
+        <v>7.4537500000000007E-2</v>
       </c>
     </row>
     <row r="274" spans="3:6" x14ac:dyDescent="0.25">
@@ -41405,7 +41406,7 @@
       </c>
       <c r="F274">
         <f t="shared" si="30"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
     </row>
     <row r="275" spans="3:6" x14ac:dyDescent="0.25">
@@ -41421,7 +41422,7 @@
       </c>
       <c r="F275">
         <f t="shared" si="30"/>
-        <v>6.953333333333335E-2</v>
+        <v>7.7355833333333332E-2</v>
       </c>
     </row>
     <row r="276" spans="3:6" x14ac:dyDescent="0.25">
@@ -41437,7 +41438,7 @@
       </c>
       <c r="F276">
         <f t="shared" si="30"/>
-        <v>6.4933333333333343E-2</v>
+        <v>7.2238333333333335E-2</v>
       </c>
     </row>
     <row r="277" spans="3:6" x14ac:dyDescent="0.25">
@@ -41453,7 +41454,7 @@
       </c>
       <c r="F277">
         <f t="shared" si="30"/>
-        <v>7.006666666666668E-2</v>
+        <v>7.7949166666666667E-2</v>
       </c>
     </row>
     <row r="278" spans="3:6" x14ac:dyDescent="0.25">
@@ -41469,7 +41470,7 @@
       </c>
       <c r="F278">
         <f t="shared" si="30"/>
-        <v>6.7000000000000018E-2</v>
+        <v>7.4537500000000007E-2</v>
       </c>
     </row>
     <row r="279" spans="3:6" x14ac:dyDescent="0.25">
@@ -41485,7 +41486,7 @@
       </c>
       <c r="F279">
         <f t="shared" si="30"/>
-        <v>6.6466666666666688E-2</v>
+        <v>7.3944166666666672E-2</v>
       </c>
     </row>
     <row r="280" spans="3:6" x14ac:dyDescent="0.25">
@@ -41501,7 +41502,7 @@
       </c>
       <c r="F280">
         <f t="shared" si="30"/>
-        <v>6.7500000000000018E-2</v>
+        <v>7.5093750000000001E-2</v>
       </c>
     </row>
     <row r="281" spans="3:6" x14ac:dyDescent="0.25">
@@ -41517,7 +41518,7 @@
       </c>
       <c r="F281">
         <f t="shared" si="30"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
     </row>
     <row r="282" spans="3:6" x14ac:dyDescent="0.25">
@@ -41533,7 +41534,7 @@
       </c>
       <c r="F282">
         <f t="shared" si="30"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
     </row>
     <row r="283" spans="3:6" x14ac:dyDescent="0.25">
@@ -41549,7 +41550,7 @@
       </c>
       <c r="F283">
         <f t="shared" si="30"/>
-        <v>5.8800000000000012E-2</v>
+        <v>6.5415000000000001E-2</v>
       </c>
     </row>
     <row r="284" spans="3:6" x14ac:dyDescent="0.25">
@@ -41565,7 +41566,7 @@
       </c>
       <c r="F284">
         <f t="shared" si="30"/>
-        <v>5.9300000000000005E-2</v>
+        <v>6.5971249999999995E-2</v>
       </c>
     </row>
     <row r="285" spans="3:6" x14ac:dyDescent="0.25">
@@ -41581,7 +41582,7 @@
       </c>
       <c r="F285">
         <f t="shared" si="30"/>
-        <v>6.8533333333333349E-2</v>
+        <v>7.624333333333333E-2</v>
       </c>
     </row>
     <row r="286" spans="3:6" x14ac:dyDescent="0.25">
@@ -41597,7 +41598,7 @@
       </c>
       <c r="F286">
         <f t="shared" si="30"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
     </row>
     <row r="287" spans="3:6" x14ac:dyDescent="0.25">
@@ -41613,7 +41614,7 @@
       </c>
       <c r="F287">
         <f t="shared" si="30"/>
-        <v>6.5466666666666687E-2</v>
+        <v>7.283166666666667E-2</v>
       </c>
     </row>
     <row r="288" spans="3:6" x14ac:dyDescent="0.25">
@@ -41629,7 +41630,7 @@
       </c>
       <c r="F288">
         <f t="shared" si="30"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
     </row>
     <row r="289" spans="3:6" x14ac:dyDescent="0.25">
@@ -41645,7 +41646,7 @@
       </c>
       <c r="F289">
         <f t="shared" si="30"/>
-        <v>5.9300000000000005E-2</v>
+        <v>6.5971249999999995E-2</v>
       </c>
     </row>
     <row r="290" spans="3:6" x14ac:dyDescent="0.25">
@@ -41661,7 +41662,7 @@
       </c>
       <c r="F290">
         <f t="shared" si="30"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="291" spans="3:6" x14ac:dyDescent="0.25">
@@ -41677,7 +41678,7 @@
       </c>
       <c r="F291">
         <f t="shared" si="30"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="292" spans="3:6" x14ac:dyDescent="0.25">
@@ -41693,7 +41694,7 @@
       </c>
       <c r="F292">
         <f t="shared" si="30"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="293" spans="3:6" x14ac:dyDescent="0.25">
@@ -41709,7 +41710,7 @@
       </c>
       <c r="F293">
         <f t="shared" si="30"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
     </row>
     <row r="294" spans="3:6" x14ac:dyDescent="0.25">
@@ -41725,7 +41726,7 @@
       </c>
       <c r="F294">
         <f t="shared" si="30"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="295" spans="3:6" x14ac:dyDescent="0.25">
@@ -41741,7 +41742,7 @@
       </c>
       <c r="F295">
         <f t="shared" si="30"/>
-        <v>6.3900000000000012E-2</v>
+        <v>7.1088750000000006E-2</v>
       </c>
     </row>
     <row r="296" spans="3:6" x14ac:dyDescent="0.25">
@@ -41757,7 +41758,7 @@
       </c>
       <c r="F296">
         <f t="shared" si="30"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="297" spans="3:6" x14ac:dyDescent="0.25">
@@ -41773,7 +41774,7 @@
       </c>
       <c r="F297">
         <f t="shared" si="30"/>
-        <v>5.8300000000000005E-2</v>
+        <v>6.4858749999999993E-2</v>
       </c>
     </row>
     <row r="298" spans="3:6" x14ac:dyDescent="0.25">
@@ -41789,7 +41790,7 @@
       </c>
       <c r="F298">
         <f t="shared" si="30"/>
-        <v>5.6766666666666681E-2</v>
+        <v>6.315291666666667E-2</v>
       </c>
     </row>
     <row r="299" spans="3:6" x14ac:dyDescent="0.25">
@@ -41805,7 +41806,7 @@
       </c>
       <c r="F299">
         <f t="shared" si="30"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="300" spans="3:6" x14ac:dyDescent="0.25">
@@ -41821,7 +41822,7 @@
       </c>
       <c r="F300">
         <f t="shared" si="30"/>
-        <v>5.2666666666666681E-2</v>
+        <v>5.8591666666666674E-2</v>
       </c>
     </row>
     <row r="301" spans="3:6" x14ac:dyDescent="0.25">
@@ -41837,7 +41838,7 @@
       </c>
       <c r="F301">
         <f t="shared" si="30"/>
-        <v>5.3700000000000012E-2</v>
+        <v>5.9741250000000003E-2</v>
       </c>
     </row>
     <row r="302" spans="3:6" x14ac:dyDescent="0.25">
@@ -41853,7 +41854,7 @@
       </c>
       <c r="F302">
         <f t="shared" si="30"/>
-        <v>5.1133333333333343E-2</v>
+        <v>5.6885833333333337E-2</v>
       </c>
     </row>
     <row r="303" spans="3:6" x14ac:dyDescent="0.25">
@@ -41869,7 +41870,7 @@
       </c>
       <c r="F303">
         <f t="shared" si="30"/>
-        <v>5.0100000000000006E-2</v>
+        <v>5.5736250000000001E-2</v>
       </c>
     </row>
     <row r="304" spans="3:6" x14ac:dyDescent="0.25">
@@ -41885,7 +41886,7 @@
       </c>
       <c r="F304">
         <f t="shared" si="30"/>
-        <v>5.9300000000000005E-2</v>
+        <v>6.5971249999999995E-2</v>
       </c>
     </row>
     <row r="305" spans="3:6" x14ac:dyDescent="0.25">
@@ -41901,7 +41902,7 @@
       </c>
       <c r="F305">
         <f t="shared" si="30"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
     </row>
     <row r="306" spans="3:6" x14ac:dyDescent="0.25">
@@ -41917,7 +41918,7 @@
       </c>
       <c r="F306">
         <f t="shared" si="30"/>
-        <v>5.5233333333333343E-2</v>
+        <v>6.144708333333334E-2</v>
       </c>
     </row>
     <row r="307" spans="3:6" x14ac:dyDescent="0.25">
@@ -41933,7 +41934,7 @@
       </c>
       <c r="F307">
         <f t="shared" si="30"/>
-        <v>5.4200000000000019E-2</v>
+        <v>6.0297500000000011E-2</v>
       </c>
     </row>
     <row r="308" spans="3:6" x14ac:dyDescent="0.25">
@@ -41949,7 +41950,7 @@
       </c>
       <c r="F308">
         <f t="shared" si="30"/>
-        <v>5.2666666666666681E-2</v>
+        <v>5.8591666666666674E-2</v>
       </c>
     </row>
     <row r="309" spans="3:6" x14ac:dyDescent="0.25">
@@ -41965,7 +41966,7 @@
       </c>
       <c r="F309">
         <f t="shared" si="30"/>
-        <v>5.5233333333333343E-2</v>
+        <v>6.144708333333334E-2</v>
       </c>
     </row>
     <row r="310" spans="3:6" x14ac:dyDescent="0.25">
@@ -41981,7 +41982,7 @@
       </c>
       <c r="F310">
         <f t="shared" si="30"/>
-        <v>5.623333333333335E-2</v>
+        <v>6.2559583333333335E-2</v>
       </c>
     </row>
     <row r="311" spans="3:6" x14ac:dyDescent="0.25">
@@ -41997,7 +41998,7 @@
       </c>
       <c r="F311">
         <f t="shared" si="30"/>
-        <v>5.5733333333333343E-2</v>
+        <v>6.2003333333333334E-2</v>
       </c>
     </row>
     <row r="312" spans="3:6" x14ac:dyDescent="0.25">
@@ -42013,7 +42014,7 @@
       </c>
       <c r="F312">
         <f t="shared" si="30"/>
-        <v>5.2666666666666681E-2</v>
+        <v>5.8591666666666674E-2</v>
       </c>
     </row>
     <row r="313" spans="3:6" x14ac:dyDescent="0.25">
@@ -42029,7 +42030,7 @@
       </c>
       <c r="F313">
         <f t="shared" si="30"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="314" spans="3:6" x14ac:dyDescent="0.25">
@@ -42045,7 +42046,7 @@
       </c>
       <c r="F314">
         <f t="shared" si="30"/>
-        <v>6.2366666666666681E-2</v>
+        <v>6.9382916666666669E-2</v>
       </c>
     </row>
     <row r="315" spans="3:6" x14ac:dyDescent="0.25">
@@ -42061,7 +42062,7 @@
       </c>
       <c r="F315">
         <f t="shared" si="30"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="316" spans="3:6" x14ac:dyDescent="0.25">
@@ -42077,7 +42078,7 @@
       </c>
       <c r="F316">
         <f t="shared" si="30"/>
-        <v>5.7766666666666674E-2</v>
+        <v>6.4265416666666658E-2</v>
       </c>
     </row>
     <row r="317" spans="3:6" x14ac:dyDescent="0.25">
@@ -42093,7 +42094,7 @@
       </c>
       <c r="F317">
         <f t="shared" si="30"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="318" spans="3:6" x14ac:dyDescent="0.25">
@@ -42109,7 +42110,7 @@
       </c>
       <c r="F318">
         <f t="shared" si="30"/>
-        <v>5.9833333333333343E-2</v>
+        <v>6.656458333333333E-2</v>
       </c>
     </row>
     <row r="319" spans="3:6" x14ac:dyDescent="0.25">
@@ -42125,7 +42126,7 @@
       </c>
       <c r="F319">
         <f t="shared" si="30"/>
-        <v>6.033333333333335E-2</v>
+        <v>6.7120833333333338E-2</v>
       </c>
     </row>
     <row r="320" spans="3:6" x14ac:dyDescent="0.25">
@@ -42141,7 +42142,7 @@
       </c>
       <c r="F320">
         <f t="shared" si="30"/>
-        <v>6.0833333333333343E-2</v>
+        <v>6.7677083333333332E-2</v>
       </c>
     </row>
     <row r="322" spans="4:6" x14ac:dyDescent="0.25">
@@ -42151,13 +42152,13 @@
       </c>
       <c r="F322">
         <f>AVERAGE(F33:F320)</f>
-        <v>6.0895601851851847E-2</v>
+        <v>6.7746357060185239E-2</v>
       </c>
     </row>
     <row r="323" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F323">
         <f>_xlfn.VAR.P(F33:F320)</f>
-        <v>3.1457712137774342E-5</v>
+        <v>3.8933834038017261E-5</v>
       </c>
     </row>
   </sheetData>
@@ -42169,15 +42170,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AE804"/>
+  <dimension ref="A2:AJ804"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -42235,8 +42237,10 @@
       <c r="AE2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4</v>
       </c>
@@ -42324,8 +42328,10 @@
         <f>AC3*($A$5/(2*PI()))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -42413,8 +42419,10 @@
         <f t="shared" ref="AE4:AE67" si="11">AC4*($A$5/(2*PI()))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI4" s="4"/>
+      <c r="AJ4" s="4"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3.2</v>
       </c>
@@ -42502,8 +42510,10 @@
         <f t="shared" si="11"/>
         <v>0.62643385600970003</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI5" s="4"/>
+      <c r="AJ5" s="4"/>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -42591,8 +42601,10 @@
         <f t="shared" si="11"/>
         <v>1.4056564573876196</v>
       </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI6" s="4"/>
+      <c r="AJ6" s="4"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>A5/A3</f>
         <v>0.8</v>
@@ -42681,8 +42693,10 @@
         <f t="shared" si="11"/>
         <v>1.9506029825342692</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI7" s="4"/>
+      <c r="AJ7" s="4"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>6000</v>
       </c>
@@ -42767,8 +42781,10 @@
         <f t="shared" si="11"/>
         <v>2.4242480931757497</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI8" s="4"/>
+      <c r="AJ8" s="4"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>7000</v>
       </c>
@@ -42853,8 +42869,10 @@
         <f t="shared" si="11"/>
         <v>2.8113129147752391</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI9" s="4"/>
+      <c r="AJ9" s="4"/>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>8000</v>
       </c>
@@ -42939,8 +42957,10 @@
         <f t="shared" si="11"/>
         <v>3.1270763218695596</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI10" s="4"/>
+      <c r="AJ10" s="4"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C11">
         <v>9000</v>
       </c>
@@ -43025,8 +43045,10 @@
         <f t="shared" si="11"/>
         <v>3.2034706945536695</v>
       </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI11" s="4"/>
+      <c r="AJ11" s="4"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>10000</v>
       </c>
@@ -43111,8 +43133,10 @@
         <f t="shared" si="11"/>
         <v>4.0641806267946397</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C13">
         <v>11000</v>
       </c>
@@ -43197,8 +43221,10 @@
         <f t="shared" si="11"/>
         <v>3.906298923247479</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI13" s="4"/>
+      <c r="AJ13" s="4"/>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C14">
         <v>12000</v>
       </c>
@@ -43283,8 +43309,10 @@
         <f t="shared" si="11"/>
         <v>4.1405749994787495</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI14" s="4"/>
+      <c r="AJ14" s="4"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C15">
         <v>13000</v>
       </c>
@@ -43369,8 +43397,10 @@
         <f t="shared" si="11"/>
         <v>4.2984567030259093</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI15" s="4"/>
+      <c r="AJ15" s="4"/>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C16">
         <v>14000</v>
       </c>
@@ -43455,8 +43485,10 @@
         <f t="shared" si="11"/>
         <v>4.3748510757100192</v>
       </c>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI16" s="4"/>
+      <c r="AJ16" s="4"/>
+    </row>
+    <row r="17" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C17">
         <v>15000</v>
       </c>
@@ -43541,8 +43573,10 @@
         <f t="shared" si="11"/>
         <v>4.3748510757100192</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI17" s="4"/>
+      <c r="AJ17" s="4"/>
+    </row>
+    <row r="18" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C18">
         <v>16000</v>
       </c>
@@ -43627,8 +43661,10 @@
         <f t="shared" si="11"/>
         <v>4.6855215246253987</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI18" s="4"/>
+      <c r="AJ18" s="4"/>
+    </row>
+    <row r="19" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C19">
         <v>17000</v>
       </c>
@@ -43713,8 +43749,10 @@
         <f t="shared" si="11"/>
         <v>5.1540736770879381</v>
       </c>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI19" s="4"/>
+      <c r="AJ19" s="4"/>
+    </row>
+    <row r="20" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C20">
         <v>18000</v>
       </c>
@@ -43799,8 +43837,10 @@
         <f t="shared" si="11"/>
         <v>5.2355610079509889</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI20" s="4"/>
+      <c r="AJ20" s="4"/>
+    </row>
+    <row r="21" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C21">
         <v>19000</v>
       </c>
@@ -43885,8 +43925,10 @@
         <f t="shared" si="11"/>
         <v>4.9197976008566684</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI21" s="4"/>
+      <c r="AJ21" s="4"/>
+    </row>
+    <row r="22" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C22">
         <v>20000</v>
       </c>
@@ -43971,8 +44013,10 @@
         <f t="shared" si="11"/>
         <v>4.8434032281725585</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI22" s="4"/>
+      <c r="AJ22" s="4"/>
+    </row>
+    <row r="23" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>21000</v>
       </c>
@@ -44057,8 +44101,10 @@
         <f t="shared" si="11"/>
         <v>5.0776793044038291</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI23" s="4"/>
+      <c r="AJ23" s="4"/>
+    </row>
+    <row r="24" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C24">
         <v>22000</v>
       </c>
@@ -44143,8 +44189,10 @@
         <f t="shared" si="11"/>
         <v>5.1540736770879381</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI24" s="4"/>
+      <c r="AJ24" s="4"/>
+    </row>
+    <row r="25" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C25">
         <v>23000</v>
       </c>
@@ -44229,8 +44277,10 @@
         <f t="shared" si="11"/>
         <v>5.0776793044038291</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI25" s="4"/>
+      <c r="AJ25" s="4"/>
+    </row>
+    <row r="26" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C26">
         <v>24000</v>
       </c>
@@ -44315,8 +44365,10 @@
         <f t="shared" si="11"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI26" s="4"/>
+      <c r="AJ26" s="4"/>
+    </row>
+    <row r="27" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C27">
         <v>25000</v>
       </c>
@@ -44401,8 +44453,10 @@
         <f t="shared" si="11"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI27" s="4"/>
+      <c r="AJ27" s="4"/>
+    </row>
+    <row r="28" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C28">
         <v>26000</v>
       </c>
@@ -44487,8 +44541,10 @@
         <f t="shared" si="11"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI28" s="4"/>
+      <c r="AJ28" s="4"/>
+    </row>
+    <row r="29" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C29">
         <v>27000</v>
       </c>
@@ -44573,8 +44629,10 @@
         <f t="shared" si="11"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI29" s="4"/>
+      <c r="AJ29" s="4"/>
+    </row>
+    <row r="30" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C30">
         <v>28000</v>
       </c>
@@ -44659,8 +44717,10 @@
         <f t="shared" si="11"/>
         <v>5.5462314568663693</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI30" s="4"/>
+      <c r="AJ30" s="4"/>
+    </row>
+    <row r="31" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C31">
         <v>29000</v>
       </c>
@@ -44745,8 +44805,10 @@
         <f t="shared" si="11"/>
         <v>5.5462314568663693</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI31" s="4"/>
+      <c r="AJ31" s="4"/>
+    </row>
+    <row r="32" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C32">
         <v>30000</v>
       </c>
@@ -44831,8 +44893,10 @@
         <f t="shared" si="11"/>
         <v>5.7041131604135282</v>
       </c>
-    </row>
-    <row r="33" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI32" s="4"/>
+      <c r="AJ32" s="4"/>
+    </row>
+    <row r="33" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C33">
         <v>31000</v>
       </c>
@@ -44917,8 +44981,10 @@
         <f t="shared" si="11"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="34" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI33" s="4"/>
+      <c r="AJ33" s="4"/>
+    </row>
+    <row r="34" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C34">
         <v>32000</v>
       </c>
@@ -45003,8 +45069,10 @@
         <f t="shared" si="11"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="35" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI34" s="4"/>
+      <c r="AJ34" s="4"/>
+    </row>
+    <row r="35" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C35">
         <v>33000</v>
       </c>
@@ -45089,8 +45157,10 @@
         <f t="shared" si="11"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="36" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI35" s="4"/>
+      <c r="AJ35" s="4"/>
+    </row>
+    <row r="36" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C36">
         <v>34000</v>
       </c>
@@ -45175,8 +45245,10 @@
         <f t="shared" si="11"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="37" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI36" s="4"/>
+      <c r="AJ36" s="4"/>
+    </row>
+    <row r="37" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C37">
         <v>35000</v>
       </c>
@@ -45261,8 +45333,10 @@
         <f t="shared" si="11"/>
         <v>5.7041131604135282</v>
       </c>
-    </row>
-    <row r="38" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI37" s="4"/>
+      <c r="AJ37" s="4"/>
+    </row>
+    <row r="38" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C38">
         <v>36000</v>
       </c>
@@ -45347,8 +45421,10 @@
         <f t="shared" si="11"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="39" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI38" s="4"/>
+      <c r="AJ38" s="4"/>
+    </row>
+    <row r="39" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C39">
         <v>37000</v>
       </c>
@@ -45433,8 +45509,10 @@
         <f t="shared" si="11"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="40" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI39" s="4"/>
+      <c r="AJ39" s="4"/>
+    </row>
+    <row r="40" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C40">
         <v>38000</v>
       </c>
@@ -45519,8 +45597,10 @@
         <f t="shared" si="11"/>
         <v>5.0776793044038291</v>
       </c>
-    </row>
-    <row r="41" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI40" s="4"/>
+      <c r="AJ40" s="4"/>
+    </row>
+    <row r="41" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C41">
         <v>39000</v>
       </c>
@@ -45605,8 +45685,10 @@
         <f t="shared" si="11"/>
         <v>5.2355610079509889</v>
       </c>
-    </row>
-    <row r="42" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI41" s="4"/>
+      <c r="AJ41" s="4"/>
+    </row>
+    <row r="42" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C42">
         <v>40000</v>
       </c>
@@ -45691,8 +45773,10 @@
         <f t="shared" si="11"/>
         <v>5.7041131604135282</v>
       </c>
-    </row>
-    <row r="43" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI42" s="4"/>
+      <c r="AJ42" s="4"/>
+    </row>
+    <row r="43" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C43">
         <v>41000</v>
       </c>
@@ -45777,8 +45861,10 @@
         <f t="shared" si="11"/>
         <v>5.5462314568663693</v>
       </c>
-    </row>
-    <row r="44" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="4"/>
+    </row>
+    <row r="44" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C44">
         <v>42000</v>
       </c>
@@ -45863,8 +45949,10 @@
         <f t="shared" si="11"/>
         <v>5.0776793044038291</v>
       </c>
-    </row>
-    <row r="45" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI44" s="4"/>
+      <c r="AJ44" s="4"/>
+    </row>
+    <row r="45" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C45">
         <v>43000</v>
       </c>
@@ -45949,8 +46037,10 @@
         <f t="shared" si="11"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="46" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI45" s="4"/>
+      <c r="AJ45" s="4"/>
+    </row>
+    <row r="46" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C46">
         <v>44000</v>
       </c>
@@ -46035,8 +46125,10 @@
         <f t="shared" si="11"/>
         <v>5.1540736770879381</v>
       </c>
-    </row>
-    <row r="47" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI46" s="4"/>
+      <c r="AJ46" s="4"/>
+    </row>
+    <row r="47" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C47">
         <v>45000</v>
       </c>
@@ -46121,8 +46213,10 @@
         <f t="shared" si="11"/>
         <v>5.5462314568663693</v>
       </c>
-    </row>
-    <row r="48" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI47" s="4"/>
+      <c r="AJ47" s="4"/>
+    </row>
+    <row r="48" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C48">
         <v>46000</v>
       </c>
@@ -46207,8 +46301,10 @@
         <f t="shared" si="11"/>
         <v>5.6226258295504783</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI48" s="4"/>
+      <c r="AJ48" s="4"/>
+    </row>
+    <row r="49" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C49">
         <v>47000</v>
       </c>
@@ -46293,8 +46389,10 @@
         <f t="shared" si="11"/>
         <v>5.2355610079509889</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI49" s="4"/>
+      <c r="AJ49" s="4"/>
+    </row>
+    <row r="50" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C50">
         <v>48000</v>
       </c>
@@ -46379,8 +46477,10 @@
         <f t="shared" si="11"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI50" s="4"/>
+      <c r="AJ50" s="4"/>
+    </row>
+    <row r="51" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C51">
         <v>49000</v>
       </c>
@@ -46465,8 +46565,10 @@
         <f t="shared" si="11"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI51" s="4"/>
+      <c r="AJ51" s="4"/>
+    </row>
+    <row r="52" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C52">
         <v>50000</v>
       </c>
@@ -46551,8 +46653,10 @@
         <f t="shared" si="11"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI52" s="4"/>
+      <c r="AJ52" s="4"/>
+    </row>
+    <row r="53" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C53">
         <v>51000</v>
       </c>
@@ -46637,8 +46741,10 @@
         <f t="shared" si="11"/>
         <v>5.8569019057817489</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI53" s="4"/>
+      <c r="AJ53" s="4"/>
+    </row>
+    <row r="54" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C54">
         <v>52000</v>
       </c>
@@ -46723,8 +46829,10 @@
         <f t="shared" si="11"/>
         <v>5.7041131604135282</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI54" s="4"/>
+      <c r="AJ54" s="4"/>
+    </row>
+    <row r="55" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C55">
         <v>53000</v>
       </c>
@@ -46809,8 +46917,10 @@
         <f t="shared" si="11"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI55" s="4"/>
+      <c r="AJ55" s="4"/>
+    </row>
+    <row r="56" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C56">
         <v>54000</v>
       </c>
@@ -46895,8 +47005,10 @@
         <f t="shared" si="11"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI56" s="4"/>
+      <c r="AJ56" s="4"/>
+    </row>
+    <row r="57" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C57">
         <v>55000</v>
       </c>
@@ -46981,8 +47093,10 @@
         <f t="shared" si="11"/>
         <v>5.0776793044038291</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI57" s="4"/>
+      <c r="AJ57" s="4"/>
+    </row>
+    <row r="58" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C58">
         <v>56000</v>
       </c>
@@ -47067,8 +47181,10 @@
         <f t="shared" si="11"/>
         <v>5.5462314568663693</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI58" s="4"/>
+      <c r="AJ58" s="4"/>
+    </row>
+    <row r="59" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C59">
         <v>57000</v>
       </c>
@@ -47153,8 +47269,10 @@
         <f t="shared" si="11"/>
         <v>5.8569019057817489</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI59" s="4"/>
+      <c r="AJ59" s="4"/>
+    </row>
+    <row r="60" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C60">
         <v>58000</v>
       </c>
@@ -47239,8 +47357,10 @@
         <f t="shared" si="11"/>
         <v>5.2355610079509889</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI60" s="4"/>
+      <c r="AJ60" s="4"/>
+    </row>
+    <row r="61" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C61">
         <v>59000</v>
       </c>
@@ -47325,8 +47445,10 @@
         <f t="shared" si="11"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI61" s="4"/>
+      <c r="AJ61" s="4"/>
+    </row>
+    <row r="62" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C62">
         <v>60000</v>
       </c>
@@ -47411,8 +47533,10 @@
         <f t="shared" si="11"/>
         <v>5.2355610079509889</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI62" s="4"/>
+      <c r="AJ62" s="4"/>
+    </row>
+    <row r="63" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C63">
         <v>61000</v>
       </c>
@@ -47497,8 +47621,10 @@
         <f t="shared" si="11"/>
         <v>5.0012849317197192</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI63" s="4"/>
+      <c r="AJ63" s="4"/>
+    </row>
+    <row r="64" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C64">
         <v>62000</v>
       </c>
@@ -47583,8 +47709,10 @@
         <f t="shared" si="11"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="65" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI64" s="4"/>
+      <c r="AJ64" s="4"/>
+    </row>
+    <row r="65" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C65">
         <v>63000</v>
       </c>
@@ -47669,8 +47797,10 @@
         <f t="shared" si="11"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="66" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI65" s="4"/>
+      <c r="AJ65" s="4"/>
+    </row>
+    <row r="66" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C66">
         <v>64000</v>
       </c>
@@ -47755,8 +47885,10 @@
         <f t="shared" si="11"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="67" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI66" s="4"/>
+      <c r="AJ66" s="4"/>
+    </row>
+    <row r="67" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C67">
         <v>65000</v>
       </c>
@@ -47841,8 +47973,10 @@
         <f t="shared" si="11"/>
         <v>5.2355610079509889</v>
       </c>
-    </row>
-    <row r="68" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI67" s="4"/>
+      <c r="AJ67" s="4"/>
+    </row>
+    <row r="68" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C68">
         <v>66000</v>
       </c>
@@ -47927,8 +48061,10 @@
         <f t="shared" ref="AE68:AE131" si="24">AC68*($A$5/(2*PI()))</f>
         <v>5.1540736770879381</v>
       </c>
-    </row>
-    <row r="69" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI68" s="4"/>
+      <c r="AJ68" s="4"/>
+    </row>
+    <row r="69" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C69">
         <v>67000</v>
       </c>
@@ -48013,8 +48149,10 @@
         <f t="shared" si="24"/>
         <v>5.5462314568663693</v>
       </c>
-    </row>
-    <row r="70" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI69" s="4"/>
+      <c r="AJ69" s="4"/>
+    </row>
+    <row r="70" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C70">
         <v>68000</v>
       </c>
@@ -48099,8 +48237,10 @@
         <f t="shared" si="24"/>
         <v>5.7041131604135282</v>
       </c>
-    </row>
-    <row r="71" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI70" s="4"/>
+      <c r="AJ70" s="4"/>
+    </row>
+    <row r="71" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C71">
         <v>69000</v>
       </c>
@@ -48185,8 +48325,10 @@
         <f t="shared" si="24"/>
         <v>5.2355610079509889</v>
       </c>
-    </row>
-    <row r="72" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI71" s="4"/>
+      <c r="AJ71" s="4"/>
+    </row>
+    <row r="72" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C72">
         <v>70000</v>
       </c>
@@ -48271,8 +48413,10 @@
         <f t="shared" si="24"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="73" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI72" s="4"/>
+      <c r="AJ72" s="4"/>
+    </row>
+    <row r="73" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C73">
         <v>71000</v>
       </c>
@@ -48357,8 +48501,10 @@
         <f t="shared" si="24"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="74" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI73" s="4"/>
+      <c r="AJ73" s="4"/>
+    </row>
+    <row r="74" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C74">
         <v>72000</v>
       </c>
@@ -48443,8 +48589,10 @@
         <f t="shared" si="24"/>
         <v>5.2355610079509889</v>
       </c>
-    </row>
-    <row r="75" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI74" s="4"/>
+      <c r="AJ74" s="4"/>
+    </row>
+    <row r="75" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C75">
         <v>73000</v>
       </c>
@@ -48529,8 +48677,10 @@
         <f t="shared" si="24"/>
         <v>5.7805075330976381</v>
       </c>
-    </row>
-    <row r="76" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI75" s="4"/>
+      <c r="AJ75" s="4"/>
+    </row>
+    <row r="76" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C76">
         <v>74000</v>
       </c>
@@ -48615,8 +48765,10 @@
         <f t="shared" si="24"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="77" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI76" s="4"/>
+      <c r="AJ76" s="4"/>
+    </row>
+    <row r="77" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C77">
         <v>75000</v>
       </c>
@@ -48687,8 +48839,10 @@
         <f t="shared" si="24"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="78" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI77" s="4"/>
+      <c r="AJ77" s="4"/>
+    </row>
+    <row r="78" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C78">
         <v>76000</v>
       </c>
@@ -48763,8 +48917,10 @@
         <f t="shared" si="24"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="79" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI78" s="4"/>
+      <c r="AJ78" s="4"/>
+    </row>
+    <row r="79" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C79">
         <v>77000</v>
       </c>
@@ -48839,8 +48995,10 @@
         <f t="shared" si="24"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="80" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI79" s="4"/>
+      <c r="AJ79" s="4"/>
+    </row>
+    <row r="80" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C80">
         <v>78000</v>
       </c>
@@ -48911,8 +49069,10 @@
         <f t="shared" si="24"/>
         <v>5.6226258295504783</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI80" s="4"/>
+      <c r="AJ80" s="4"/>
+    </row>
+    <row r="81" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C81">
         <v>79000</v>
       </c>
@@ -48983,8 +49143,10 @@
         <f t="shared" si="24"/>
         <v>5.7805075330976381</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI81" s="4"/>
+      <c r="AJ81" s="4"/>
+    </row>
+    <row r="82" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C82">
         <v>80000</v>
       </c>
@@ -49055,8 +49217,10 @@
         <f t="shared" si="24"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI82" s="4"/>
+      <c r="AJ82" s="4"/>
+    </row>
+    <row r="83" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C83">
         <v>81000</v>
       </c>
@@ -49127,8 +49291,10 @@
         <f t="shared" si="24"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI83" s="4"/>
+      <c r="AJ83" s="4"/>
+    </row>
+    <row r="84" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C84">
         <v>82000</v>
       </c>
@@ -49199,8 +49365,10 @@
         <f t="shared" si="24"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI84" s="4"/>
+      <c r="AJ84" s="4"/>
+    </row>
+    <row r="85" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C85">
         <v>83000</v>
       </c>
@@ -49271,8 +49439,10 @@
         <f t="shared" si="24"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI85" s="4"/>
+      <c r="AJ85" s="4"/>
+    </row>
+    <row r="86" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C86">
         <v>84000</v>
       </c>
@@ -49343,8 +49513,10 @@
         <f t="shared" si="24"/>
         <v>5.9383892366447988</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI86" s="4"/>
+      <c r="AJ86" s="4"/>
+    </row>
+    <row r="87" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C87">
         <v>85000</v>
       </c>
@@ -49415,8 +49587,10 @@
         <f t="shared" si="24"/>
         <v>5.5462314568663693</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI87" s="4"/>
+      <c r="AJ87" s="4"/>
+    </row>
+    <row r="88" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C88">
         <v>86000</v>
       </c>
@@ -49487,8 +49661,10 @@
         <f t="shared" si="24"/>
         <v>5.1540736770879381</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI88" s="4"/>
+      <c r="AJ88" s="4"/>
+    </row>
+    <row r="89" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C89">
         <v>87000</v>
       </c>
@@ -49559,8 +49735,10 @@
         <f t="shared" si="24"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI89" s="4"/>
+      <c r="AJ89" s="4"/>
+    </row>
+    <row r="90" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C90">
         <v>88000</v>
       </c>
@@ -49631,8 +49809,10 @@
         <f t="shared" si="24"/>
         <v>5.5462314568663693</v>
       </c>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI90" s="4"/>
+      <c r="AJ90" s="4"/>
+    </row>
+    <row r="91" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C91">
         <v>89000</v>
       </c>
@@ -49703,8 +49883,10 @@
         <f t="shared" si="24"/>
         <v>5.8569019057817489</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI91" s="4"/>
+      <c r="AJ91" s="4"/>
+    </row>
+    <row r="92" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C92">
         <v>90000</v>
       </c>
@@ -49775,8 +49957,10 @@
         <f t="shared" si="24"/>
         <v>5.7041131604135282</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI92" s="4"/>
+      <c r="AJ92" s="4"/>
+    </row>
+    <row r="93" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C93">
         <v>91000</v>
       </c>
@@ -49847,8 +50031,10 @@
         <f t="shared" si="24"/>
         <v>5.3883497533192086</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI93" s="4"/>
+      <c r="AJ93" s="4"/>
+    </row>
+    <row r="94" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C94">
         <v>92000</v>
       </c>
@@ -49919,8 +50105,10 @@
         <f t="shared" si="24"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI94" s="4"/>
+      <c r="AJ94" s="4"/>
+    </row>
+    <row r="95" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C95">
         <v>93000</v>
       </c>
@@ -49991,8 +50179,10 @@
         <f t="shared" si="24"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI95" s="4"/>
+      <c r="AJ95" s="4"/>
+    </row>
+    <row r="96" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C96">
         <v>94000</v>
       </c>
@@ -50063,8 +50253,10 @@
         <f t="shared" si="24"/>
         <v>5.4698370841822594</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI96" s="4"/>
+      <c r="AJ96" s="4"/>
+    </row>
+    <row r="97" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C97">
         <v>95000</v>
       </c>
@@ -50135,8 +50327,10 @@
         <f t="shared" si="24"/>
         <v>6.0147836093289087</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI97" s="4"/>
+      <c r="AJ97" s="4"/>
+    </row>
+    <row r="98" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C98">
         <v>96000</v>
       </c>
@@ -50207,8 +50401,10 @@
         <f t="shared" si="24"/>
         <v>5.7041131604135282</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI98" s="4"/>
+      <c r="AJ98" s="4"/>
+    </row>
+    <row r="99" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C99">
         <v>97000</v>
       </c>
@@ -50279,8 +50475,10 @@
         <f t="shared" si="24"/>
         <v>5.3119553806350988</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI99" s="4"/>
+      <c r="AJ99" s="4"/>
+    </row>
+    <row r="100" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C100">
         <v>98000</v>
       </c>
@@ -50351,8 +50549,10 @@
         <f t="shared" si="24"/>
         <v>5.2355610079509889</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI100" s="4"/>
+      <c r="AJ100" s="4"/>
+    </row>
+    <row r="101" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C101">
         <v>99000</v>
       </c>
@@ -50423,8 +50623,10 @@
         <f t="shared" si="24"/>
         <v>5.7041131604135282</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI101" s="4"/>
+      <c r="AJ101" s="4"/>
+    </row>
+    <row r="102" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C102">
         <v>100000</v>
       </c>
@@ -50481,8 +50683,10 @@
         <f t="shared" si="24"/>
         <v>6.0147836093289087</v>
       </c>
-    </row>
-    <row r="103" spans="3:31" x14ac:dyDescent="0.25">
+      <c r="AI102" s="4"/>
+      <c r="AJ102" s="4"/>
+    </row>
+    <row r="103" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C103">
         <v>101000</v>
       </c>
@@ -50544,7 +50748,7 @@
         <v>5.3883497533192086</v>
       </c>
     </row>
-    <row r="104" spans="3:31" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C104">
         <v>102000</v>
       </c>
@@ -50606,7 +50810,7 @@
         <v>5.0776793044038291</v>
       </c>
     </row>
-    <row r="105" spans="3:31" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C105">
         <v>103000</v>
       </c>
@@ -50664,7 +50868,7 @@
         <v>5.7041131604135282</v>
       </c>
     </row>
-    <row r="106" spans="3:31" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C106">
         <v>104000</v>
       </c>
@@ -50722,7 +50926,7 @@
         <v>5.7805075330976381</v>
       </c>
     </row>
-    <row r="107" spans="3:31" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C107">
         <v>105000</v>
       </c>
@@ -50780,7 +50984,7 @@
         <v>5.3119553806350988</v>
       </c>
     </row>
-    <row r="108" spans="3:31" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C108">
         <v>106000</v>
       </c>
@@ -50838,7 +51042,7 @@
         <v>5.8569019057817489</v>
       </c>
     </row>
-    <row r="109" spans="3:31" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C109">
         <v>107000</v>
       </c>
@@ -50896,7 +51100,7 @@
         <v>5.7805075330976381</v>
       </c>
     </row>
-    <row r="110" spans="3:31" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C110">
         <v>108000</v>
       </c>
@@ -50954,7 +51158,7 @@
         <v>5.5462314568663693</v>
       </c>
     </row>
-    <row r="111" spans="3:31" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C111">
         <v>109000</v>
       </c>
@@ -51012,7 +51216,7 @@
         <v>5.3883497533192086</v>
       </c>
     </row>
-    <row r="112" spans="3:31" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C112">
         <v>110000</v>
       </c>
@@ -67494,7 +67698,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>